--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Marchese_2021_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Marchese_2021_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{8C94FA30-1442-A847-B461-8BCABFE5E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32AFFADF-2F08-4B85-9DC4-EA34F3A8C042}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -779,7 +779,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -824,12 +824,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C18" s="4">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C32" s="4">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -3412,23 +3412,23 @@
       </c>
       <c r="B41" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$19) / 10^6</f>
-        <v>276.91199999999998</v>
+        <v>296.13600000000002</v>
       </c>
       <c r="C41" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$19) / 10^6</f>
-        <v>276.91199999999998</v>
+        <v>296.13600000000002</v>
       </c>
       <c r="D41" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$19) / 10^6</f>
-        <v>276.91199999999998</v>
+        <v>296.13600000000002</v>
       </c>
       <c r="E41" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$19) / 10^6</f>
-        <v>276.91199999999998</v>
+        <v>296.13600000000002</v>
       </c>
       <c r="F41" s="14">
         <f>(Inputs!$C$32*'Study Parameters'!$C$19) / 10^6</f>
-        <v>276.91199999999998</v>
+        <v>296.13600000000002</v>
       </c>
       <c r="G41" t="s">
         <v>96</v>
@@ -3492,23 +3492,23 @@
       </c>
       <c r="M42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>103.68</v>
+        <v>112.968</v>
       </c>
       <c r="N42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>103.68</v>
+        <v>112.968</v>
       </c>
       <c r="O42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>103.68</v>
+        <v>112.968</v>
       </c>
       <c r="P42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>103.68</v>
+        <v>112.968</v>
       </c>
       <c r="Q42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>103.68</v>
+        <v>112.968</v>
       </c>
       <c r="R42" t="s">
         <v>96</v>
@@ -20800,103 +20800,103 @@
       </c>
       <c r="C4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="D4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="E4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="F4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="G4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="H4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="I4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="J4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="K4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="L4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="M4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="N4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="O4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="P4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Q4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="R4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="S4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="T4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="U4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="V4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="W4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="X4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Y4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Z4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="AA4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -21017,103 +21017,103 @@
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -21126,103 +21126,103 @@
       </c>
       <c r="C7">
         <f>C6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>446558935.81970882</v>
+        <v>464441726.51738322</v>
       </c>
       <c r="D7">
         <f>D6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>415403661.22763616</v>
+        <v>432038815.3650077</v>
       </c>
       <c r="E7">
         <f>E6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>386422010.44431269</v>
+        <v>401896572.43256527</v>
       </c>
       <c r="F7">
         <f>F6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>359462335.29703504</v>
+        <v>373857276.68145609</v>
       </c>
       <c r="G7">
         <f>G6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>334383567.71817213</v>
+        <v>347774210.86647075</v>
       </c>
       <c r="H7">
         <f>H6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>311054481.59829968</v>
+        <v>323510893.82927519</v>
       </c>
       <c r="I7">
         <f>I6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>289353006.13795322</v>
+        <v>300940366.35281408</v>
       </c>
       <c r="J7">
         <f>J6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>269165587.10507274</v>
+        <v>279944526.83982706</v>
       </c>
       <c r="K7">
         <f>K6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>250386592.65588161</v>
+        <v>260413513.33937404</v>
       </c>
       <c r="L7">
         <f>L6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>232917760.6101225</v>
+        <v>242245128.68778986</v>
       </c>
       <c r="M7">
         <f>M6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>216667684.288486</v>
+        <v>225344305.75608355</v>
       </c>
       <c r="N7">
         <f>N6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>201551334.22184747</v>
+        <v>209622610.00565913</v>
       </c>
       <c r="O7">
         <f>O6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>187489613.22962552</v>
+        <v>194997776.74945033</v>
       </c>
       <c r="P7">
         <f>P6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>174408942.53918657</v>
+        <v>181393280.69716311</v>
       </c>
       <c r="Q7">
         <f>Q6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>162240876.78063866</v>
+        <v>168737935.53224477</v>
       </c>
       <c r="R7">
         <f>R6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>150921745.84245458</v>
+        <v>156965521.42534396</v>
       </c>
       <c r="S7">
         <f>S6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>140392321.71391124</v>
+        <v>146014438.5352037</v>
       </c>
       <c r="T7">
         <f>T6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>130597508.57108024</v>
+        <v>135827384.68391043</v>
       </c>
       <c r="U7">
         <f>U6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>121486054.48472579</v>
+        <v>126351055.51991668</v>
       </c>
       <c r="V7">
         <f>V6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>113010283.2416054</v>
+        <v>117535865.59992249</v>
       </c>
       <c r="W7">
         <f>W6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>105125844.87591198</v>
+        <v>109335688.93016045</v>
       </c>
       <c r="X7">
         <f>X6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>97791483.605499536</v>
+        <v>101707617.60945159</v>
       </c>
       <c r="Y7">
         <f>Y6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>90968821.958604217</v>
+        <v>94611737.311117753</v>
       </c>
       <c r="Z7">
         <f>Z6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>84622159.9614923</v>
+        <v>88010918.428946763</v>
       </c>
       <c r="AA7">
         <f>AA6/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>78718288.336271897</v>
+        <v>81870621.794369072</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="B11">
         <f>SUM(B7:AA7) / SUM(C9:AA9)</f>
-        <v>8.3625051596323114</v>
+        <v>8.6387120561840351</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="B12">
         <f>B11 * Inputs!$C$15</f>
-        <v>6.7150916431847465</v>
+        <v>6.9368857811157802</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -21474,103 +21474,103 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -21691,103 +21691,103 @@
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="E17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="I17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="K17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="L17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="M17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="O17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Q17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="R17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="S17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="T17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="U17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="V17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="W17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="X17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Y17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Z17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="AA17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -21800,103 +21800,103 @@
       </c>
       <c r="C18">
         <f>C17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>292211757.30172515</v>
+        <v>310094547.99939954</v>
       </c>
       <c r="D18">
         <f>D17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>271824890.51323271</v>
+        <v>288460044.65060425</v>
       </c>
       <c r="E18">
         <f>E17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>252860363.26812345</v>
+        <v>268334925.25637606</v>
       </c>
       <c r="F18">
         <f>F17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>235218942.57499856</v>
+        <v>249613883.95941958</v>
       </c>
       <c r="G18">
         <f>G17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>218808318.67441726</v>
+        <v>232198961.82271588</v>
       </c>
       <c r="H18">
         <f>H17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>203542622.02271375</v>
+        <v>215999034.25368923</v>
       </c>
       <c r="I18">
         <f>I17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>189341973.97461742</v>
+        <v>200929334.18947834</v>
       </c>
       <c r="J18">
         <f>J17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>176132068.81359762</v>
+        <v>186911008.54835194</v>
       </c>
       <c r="K18">
         <f>K17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>163843784.94288149</v>
+        <v>173870705.62637392</v>
       </c>
       <c r="L18">
         <f>L17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>152412823.2026805</v>
+        <v>161740191.28034785</v>
       </c>
       <c r="M18">
         <f>M17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>141779370.42109811</v>
+        <v>150455991.88869566</v>
       </c>
       <c r="N18">
         <f>N17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>131887786.43823081</v>
+        <v>139959062.22204247</v>
       </c>
       <c r="O18">
         <f>O17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>122686312.9657961</v>
+        <v>130194476.4856209</v>
       </c>
       <c r="P18">
         <f>P17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>114126802.75888011</v>
+        <v>121111140.91685666</v>
       </c>
       <c r="Q18">
         <f>Q17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>106164467.68267916</v>
+        <v>112661526.43428527</v>
       </c>
       <c r="R18">
         <f>R17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>98757644.35598062</v>
+        <v>104801419.93887003</v>
       </c>
       <c r="S18">
         <f>S17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>91867576.145098269</v>
+        <v>97489692.966390729</v>
       </c>
       <c r="T18">
         <f>T17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>85458210.367533267</v>
+        <v>90688086.480363473</v>
       </c>
       <c r="U18">
         <f>U17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>79496009.644216999</v>
+        <v>84361010.67940788</v>
       </c>
       <c r="V18">
         <f>V17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>73949776.413225114</v>
+        <v>78475358.771542221</v>
       </c>
       <c r="W18">
         <f>W17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>68790489.686721027</v>
+        <v>73000333.740969494</v>
       </c>
       <c r="X18">
         <f>X17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>63991153.196949802</v>
+        <v>67907287.200901866</v>
       </c>
       <c r="Y18">
         <f>Y17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>59526654.136697486</v>
+        <v>63169569.489211038</v>
       </c>
       <c r="Z18">
         <f>Z17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>55373631.755067438</v>
+        <v>58762390.222521901</v>
       </c>
       <c r="AA18">
         <f>AA17/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>51510355.120992959</v>
+        <v>54662688.579090133</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="B22">
         <f>SUM(B18:AA18) / SUM(C20:AA20)</f>
-        <v>13.86947420553355</v>
+        <v>14.556045634104979</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="B23">
         <f>B22 * Inputs!$C$15</f>
-        <v>11.137187787043441</v>
+        <v>11.688504644186299</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
@@ -22148,103 +22148,103 @@
       </c>
       <c r="C26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="D26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="E26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="F26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="G26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="H26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="I26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="J26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="K26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="L26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="M26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="N26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="O26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="P26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Q26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="R26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="S26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="T26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="U26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="V26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="W26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="X26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Y26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Z26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="AA26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
@@ -22365,103 +22365,103 @@
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="E28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="F28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="G28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="I28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="J28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="L28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="M28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="N28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="O28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="P28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Q28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="R28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="S28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="T28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="U28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="V28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="W28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="X28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Y28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Z28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="AA28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
@@ -22474,103 +22474,103 @@
       </c>
       <c r="C29">
         <f>C28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>412982398.72231942</v>
+        <v>430865189.41999394</v>
       </c>
       <c r="D29">
         <f>D28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>384169673.23006463</v>
+        <v>400804827.36743623</v>
       </c>
       <c r="E29">
         <f>E28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>357367137.8884322</v>
+        <v>372841699.8766849</v>
       </c>
       <c r="F29">
         <f>F28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>332434546.87296021</v>
+        <v>346829488.25738126</v>
       </c>
       <c r="G29">
         <f>G28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>309241438.9515909</v>
+        <v>322632082.09988958</v>
       </c>
       <c r="H29">
         <f>H28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>287666454.83868921</v>
+        <v>300122867.06966472</v>
       </c>
       <c r="I29">
         <f>I28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>267596702.17552483</v>
+        <v>279184062.39038581</v>
       </c>
       <c r="J29">
         <f>J28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>248927164.81444174</v>
+        <v>259706104.54919609</v>
       </c>
       <c r="K29">
         <f>K28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>231560153.31575975</v>
+        <v>241587073.99925217</v>
       </c>
       <c r="L29">
         <f>L28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>215404793.78210214</v>
+        <v>224732161.85976952</v>
       </c>
       <c r="M29">
         <f>M28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>200376552.35544381</v>
+        <v>209053173.82304138</v>
       </c>
       <c r="N29">
         <f>N28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>186396792.88878495</v>
+        <v>194468068.67259663</v>
       </c>
       <c r="O29">
         <f>O28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>173392365.47793949</v>
+        <v>180900528.99776432</v>
       </c>
       <c r="P29">
         <f>P28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>161295223.70040885</v>
+        <v>168279561.85838541</v>
       </c>
       <c r="Q29">
         <f>Q28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>150042068.55851984</v>
+        <v>156539127.31012598</v>
       </c>
       <c r="R29">
         <f>R28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>139574017.26373941</v>
+        <v>145617792.84662881</v>
       </c>
       <c r="S29">
         <f>S28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>129836295.12905993</v>
+        <v>135458411.9503524</v>
       </c>
       <c r="T29">
         <f>T28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>120777948.95726505</v>
+        <v>126007825.07009526</v>
       </c>
       <c r="U29">
         <f>U28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>112351580.42536283</v>
+        <v>117216581.46055372</v>
       </c>
       <c r="V29">
         <f>V28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>104513098.07010497</v>
+        <v>109038680.42842208</v>
       </c>
       <c r="W29">
         <f>W28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>97221486.576841816</v>
+        <v>101431330.6310903</v>
       </c>
       <c r="X29">
         <f>X28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>90438592.164504021</v>
+        <v>94354726.168456092</v>
       </c>
       <c r="Y29">
         <f>Y28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>84128922.943724677</v>
+        <v>87771838.296238229</v>
       </c>
       <c r="Z29">
         <f>Z28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>78259463.203464821</v>
+        <v>81648221.670919284</v>
       </c>
       <c r="AA29">
         <f>AA28/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>72799500.65438588</v>
+        <v>75951834.112483054</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
@@ -22795,7 +22795,7 @@
       </c>
       <c r="B33">
         <f>SUM(B29:AA29) / SUM(C31:AA31)</f>
-        <v>13.633649367179677</v>
+        <v>14.134274367179685</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="B34">
         <f>B33 * Inputs!$C$15</f>
-        <v>10.94782044184528</v>
+        <v>11.349822316845287</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -22822,103 +22822,103 @@
       </c>
       <c r="C37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="D37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="E37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="F37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="G37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="H37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="I37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="J37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="K37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="L37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="M37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="N37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="O37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="P37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Q37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="R37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="S37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="T37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="U37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="V37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="W37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="X37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Y37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Z37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="AA37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
@@ -23039,103 +23039,103 @@
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="D39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="E39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="F39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="G39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="H39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="I39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="J39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="K39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="L39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="M39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="N39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="O39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="P39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Q39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="R39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="S39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="T39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="U39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="V39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="W39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="X39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Y39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Z39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="AA39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
@@ -23148,103 +23148,103 @@
       </c>
       <c r="C40">
         <f>C39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>340515516.53424174</v>
+        <v>358398307.23191625</v>
       </c>
       <c r="D40">
         <f>D39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>316758620.03185278</v>
+        <v>333393774.16922444</v>
       </c>
       <c r="E40">
         <f>E39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>294659181.42497939</v>
+        <v>310133743.41323203</v>
       </c>
       <c r="F40">
         <f>F39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>274101564.11625987</v>
+        <v>288496505.50068092</v>
       </c>
       <c r="G40">
         <f>G39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>254978199.17791617</v>
+        <v>268368842.32621482</v>
       </c>
       <c r="H40">
         <f>H39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>237189022.49108481</v>
+        <v>249645434.72206035</v>
       </c>
       <c r="I40">
         <f>I39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>220640951.1544975</v>
+        <v>232228311.36935845</v>
       </c>
       <c r="J40">
         <f>J39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>205247396.42278838</v>
+        <v>216026336.15754274</v>
       </c>
       <c r="K40">
         <f>K39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>190927810.62584966</v>
+        <v>200954731.30934209</v>
       </c>
       <c r="L40">
         <f>L39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>177607265.69846484</v>
+        <v>186934633.77613223</v>
       </c>
       <c r="M40">
         <f>M39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>165216061.114851</v>
+        <v>173892682.58244854</v>
       </c>
       <c r="N40">
         <f>N39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>153689359.17660558</v>
+        <v>161760634.96041727</v>
       </c>
       <c r="O40">
         <f>O39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>142966845.74567959</v>
+        <v>150475009.26550442</v>
       </c>
       <c r="P40">
         <f>P39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>132992414.64714383</v>
+        <v>139976752.80512041</v>
       </c>
       <c r="Q40">
         <f>Q39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>123713874.09036635</v>
+        <v>130210932.84197247</v>
       </c>
       <c r="R40">
         <f>R39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>115082673.57243381</v>
+        <v>121126449.15532324</v>
       </c>
       <c r="S40">
         <f>S39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>107053649.83482216</v>
+        <v>112675766.65611465</v>
       </c>
       <c r="T40">
         <f>T39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>99584790.544020623</v>
+        <v>104814666.65685084</v>
       </c>
       <c r="U40">
         <f>U39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>92637014.459554061</v>
+        <v>97502015.494744956</v>
       </c>
       <c r="V40">
         <f>V39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>86173966.939120069</v>
+        <v>90699549.297437176</v>
       </c>
       <c r="W40">
         <f>W39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>80161829.71080935</v>
+        <v>84371673.765057832</v>
       </c>
       <c r="X40">
         <f>X39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>74569143.917031959</v>
+        <v>78485277.92098403</v>
       </c>
       <c r="Y40">
         <f>Y39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>69366645.504215777</v>
+        <v>73009560.856729344</v>
       </c>
       <c r="Z40">
         <f>Z39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>64527112.096944921</v>
+        <v>67915870.564399391</v>
       </c>
       <c r="AA40">
         <f>AA39/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>60025220.555297591</v>
+        <v>63177554.013394773</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="B44">
         <f>SUM(B40:AA40) / SUM(C42:AA42)</f>
-        <v>8.0045746551514174</v>
+        <v>8.3528355247166335</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="B45">
         <f>B44 * Inputs!$C$15</f>
-        <v>6.4276734480865887</v>
+        <v>6.7073269263474566</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
@@ -23496,103 +23496,103 @@
       </c>
       <c r="C48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="D48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="E48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="F48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="G48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="H48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="I48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="J48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="K48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="L48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="M48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="N48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="O48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="P48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Q48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="R48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="S48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="T48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="U48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="V48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="W48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="X48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Y48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Z48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="AA48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
@@ -23713,103 +23713,103 @@
       </c>
       <c r="C50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="D50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="E50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="F50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="G50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="H50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="I50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="J50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="K50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="L50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="M50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="N50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="O50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="P50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Q50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="R50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="S50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="T50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="U50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="V50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="W50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="X50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Y50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Z50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="AA50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
@@ -23822,103 +23822,103 @@
       </c>
       <c r="C51">
         <f>C50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>348608506.02161109</v>
+        <v>366491296.71928555</v>
       </c>
       <c r="D51">
         <f>D50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>324286982.34568477</v>
+        <v>340922136.48305637</v>
       </c>
       <c r="E51">
         <f>E50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>301662309.15877652</v>
+        <v>317136871.14702916</v>
       </c>
       <c r="F51">
         <f>F50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>280616101.5430479</v>
+        <v>295011042.92746902</v>
       </c>
       <c r="G51">
         <f>G50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>261038233.99353296</v>
+        <v>274428877.14183164</v>
       </c>
       <c r="H51">
         <f>H50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>242826264.18003067</v>
+        <v>255282676.41100618</v>
       </c>
       <c r="I51">
         <f>I50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>225884896.91165644</v>
+        <v>237472257.12651739</v>
       </c>
       <c r="J51">
         <f>J50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>210125485.4992153</v>
+        <v>220904425.23396966</v>
       </c>
       <c r="K51">
         <f>K50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>195465567.90624678</v>
+        <v>205492488.58973923</v>
       </c>
       <c r="L51">
         <f>L50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>181828435.26162496</v>
+        <v>191155803.33929235</v>
       </c>
       <c r="M51">
         <f>M50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>169142730.47593015</v>
+        <v>177819351.94352773</v>
       </c>
       <c r="N51">
         <f>N50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>157342074.86133039</v>
+        <v>165413350.64514208</v>
       </c>
       <c r="O51">
         <f>O50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>146364720.80123758</v>
+        <v>153872884.32106239</v>
       </c>
       <c r="P51">
         <f>P50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>136153228.65231404</v>
+        <v>143137566.8102906</v>
       </c>
       <c r="Q51">
         <f>Q50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>126654166.1881991</v>
+        <v>133151224.93980522</v>
       </c>
       <c r="R51">
         <f>R50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>117817829.01227824</v>
+        <v>123861604.59516765</v>
       </c>
       <c r="S51">
         <f>S50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>109597980.4765379</v>
+        <v>115220097.29783039</v>
       </c>
       <c r="T51">
         <f>T50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>101951609.74561666</v>
+        <v>107181485.85844688</v>
       </c>
       <c r="U51">
         <f>U50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>94838706.74010852</v>
+        <v>99703707.775299415</v>
       </c>
       <c r="V51">
         <f>V50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>88222052.781496301</v>
+        <v>92747635.139813408</v>
       </c>
       <c r="W51">
         <f>W50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>82067025.843252361</v>
+        <v>86276869.897500843</v>
       </c>
       <c r="X51">
         <f>X50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>76341419.389071971</v>
+        <v>80257553.393024042</v>
       </c>
       <c r="Y51">
         <f>Y50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>71015273.850299507</v>
+        <v>74658189.202813059</v>
       </c>
       <c r="Z51">
         <f>Z50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>66060719.860743739</v>
+        <v>69449478.328198209</v>
       </c>
       <c r="AA51">
         <f>AA50/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>61451832.428598821</v>
+        <v>64604165.886696003</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="B55">
         <f>SUM(B51:AA51) / SUM(C53:AA53)</f>
-        <v>8.4516426299364689</v>
+        <v>8.805024982877649</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
@@ -24152,7 +24152,7 @@
       </c>
       <c r="B56">
         <f>B55 * Inputs!$C$15</f>
-        <v>6.7866690318389846</v>
+        <v>7.0704350612507527</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
@@ -24175,103 +24175,103 @@
       </c>
       <c r="C60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="D60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="E60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="F60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="G60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="H60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="I60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="J60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="K60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="L60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="M60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="N60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="O60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="P60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Q60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="R60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="S60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="T60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="U60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="V60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="W60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="X60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Y60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Z60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="AA60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
@@ -24392,103 +24392,103 @@
       </c>
       <c r="C62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="D62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="E62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="F62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="G62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="H62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="I62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="J62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="K62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="L62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="M62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="N62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="O62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="P62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Q62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="R62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="S62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="T62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="U62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="V62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="W62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="X62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Y62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Z62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="AA62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -24501,103 +24501,103 @@
       </c>
       <c r="C63">
         <f>C62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>101873253.37308222</v>
+        <v>110513253.37308225</v>
       </c>
       <c r="D63">
         <f>D62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>94765817.091239274</v>
+        <v>102803026.39356488</v>
       </c>
       <c r="E63">
         <f>E62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>88154248.456966773</v>
+        <v>95630722.226571992</v>
       </c>
       <c r="F63">
         <f>F62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>82003952.052992344</v>
+        <v>88958811.373555332</v>
       </c>
       <c r="G63">
         <f>G62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>76282746.095806822</v>
+        <v>82752382.673074722</v>
       </c>
       <c r="H63">
         <f>H62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>70960694.042611018</v>
+        <v>76978960.626116037</v>
       </c>
       <c r="I63">
         <f>I62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>66009947.946614891</v>
+        <v>71608335.466154441</v>
       </c>
       <c r="J63">
         <f>J62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>61404602.741037108</v>
+        <v>66612405.084794842</v>
       </c>
       <c r="K63">
         <f>K62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>57120560.689336844</v>
+        <v>61965027.985855661</v>
       </c>
       <c r="L63">
         <f>L62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>53135405.29240638</v>
+        <v>57641886.498470396</v>
       </c>
       <c r="M63">
         <f>M62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>49428283.992936164</v>
+        <v>53620359.533460826</v>
       </c>
       <c r="N63">
         <f>N62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>45979799.063196428</v>
+        <v>49879404.217172861</v>
       </c>
       <c r="O63">
         <f>O62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>42771906.105299003</v>
+        <v>46399445.783416614</v>
       </c>
       <c r="P63">
         <f>P62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>39787819.632836282</v>
+        <v>43162275.147364296</v>
       </c>
       <c r="Q63">
         <f>Q62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>37011925.239847705</v>
+        <v>40150953.625455163</v>
       </c>
       <c r="R63">
         <f>R62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>34429697.897532754</v>
+        <v>37349724.302748986</v>
       </c>
       <c r="S63">
         <f>S62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>32027625.951193262</v>
+        <v>34743929.583952554</v>
       </c>
       <c r="T63">
         <f>T62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>29793140.419714663</v>
+        <v>32319934.496700048</v>
       </c>
       <c r="U63">
         <f>U62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>27714549.227641545</v>
+        <v>30065055.345767487</v>
       </c>
       <c r="V63">
         <f>V62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>25780976.025713068</v>
+        <v>27967493.34489999</v>
       </c>
       <c r="W63">
         <f>W62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>23982303.279733084</v>
+        <v>26016272.878976729</v>
       </c>
       <c r="X63">
         <f>X62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>22309119.329984266</v>
+        <v>24201184.073466729</v>
       </c>
       <c r="Y63">
         <f>Y62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>20752669.144171409</v>
+        <v>22512729.370666724</v>
       </c>
       <c r="Z63">
         <f>Z62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>19304808.506205965</v>
+        <v>20942073.833178349</v>
       </c>
       <c r="AA63">
         <f>AA62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>17957961.401121825</v>
+        <v>19480998.91458451</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="B67">
         <f>SUM(B63:AA63) / SUM(C65:AA65)</f>
-        <v>2.125400243913151</v>
+        <v>2.2588485197752202</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="B68">
         <f>B67 * Inputs!$C$15</f>
-        <v>1.7066963958622603</v>
+        <v>1.8138553613795019</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
@@ -24850,103 +24850,103 @@
       </c>
       <c r="C71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="D71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="E71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="F71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="G71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="H71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="I71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="J71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="K71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="L71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="M71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="N71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="O71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="P71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Q71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="R71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="S71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="T71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="U71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="V71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="W71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="X71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Y71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Z71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="AA71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
@@ -25067,103 +25067,103 @@
       </c>
       <c r="C73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="D73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="G73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="H73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="I73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="J73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="K73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="L73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="M73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="N73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="O73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="P73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Q73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="R73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="S73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="T73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="U73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="V73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="W73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="X73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Y73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Z73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="AA73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
@@ -25176,103 +25176,103 @@
       </c>
       <c r="C74">
         <f>C73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>132680587.87925729</v>
+        <v>141320587.87925726</v>
       </c>
       <c r="D74">
         <f>D73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>123423802.67837888</v>
+        <v>131461011.98070444</v>
       </c>
       <c r="E74">
         <f>E73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>114812839.70081757</v>
+        <v>122289313.47042273</v>
       </c>
       <c r="F74">
         <f>F73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>106802641.58215587</v>
+        <v>113757500.90271883</v>
       </c>
       <c r="G74">
         <f>G73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>99351294.495028719</v>
+        <v>105820931.07229657</v>
       </c>
       <c r="H74">
         <f>H73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>92419808.832584873</v>
+        <v>98438075.416089848</v>
       </c>
       <c r="I74">
         <f>I73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>85971915.193102196</v>
+        <v>91570302.712641716</v>
       </c>
       <c r="J74">
         <f>J73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>79973874.598234609</v>
+        <v>85181676.941992298</v>
       </c>
       <c r="K74">
         <f>K73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>74394301.951846138</v>
+        <v>79238769.248364925</v>
       </c>
       <c r="L74">
         <f>L73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>69204001.815670848</v>
+        <v>73710483.021734834</v>
       </c>
       <c r="M74">
         <f>M73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>64375815.642484501</v>
+        <v>68567891.183009133</v>
       </c>
       <c r="N74">
         <f>N73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>59884479.667427443</v>
+        <v>63784084.821403854</v>
       </c>
       <c r="O74">
         <f>O73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>55706492.713885993</v>
+        <v>59334032.392003581</v>
       </c>
       <c r="P74">
         <f>P73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>51819993.222219527</v>
+        <v>55194448.736747518</v>
       </c>
       <c r="Q74">
         <f>Q73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>48204644.857878633</v>
+        <v>51343673.243486069</v>
       </c>
       <c r="R74">
         <f>R73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>44841530.10035222</v>
+        <v>47761556.505568437</v>
       </c>
       <c r="S74">
         <f>S73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>41713051.256141603</v>
+        <v>44429354.888900876</v>
       </c>
       <c r="T74">
         <f>T73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>38802838.377806142</v>
+        <v>41329632.454791516</v>
       </c>
       <c r="U74">
         <f>U73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>36095663.607261531</v>
+        <v>38446169.725387454</v>
       </c>
       <c r="V74">
         <f>V73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>33577361.495127007</v>
+        <v>35763878.814313911</v>
       </c>
       <c r="W74">
         <f>W73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>31234754.879187908</v>
+        <v>33268724.478431541</v>
       </c>
       <c r="X74">
         <f>X73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>29055585.934128288</v>
+        <v>30947650.67761074</v>
       </c>
       <c r="Y74">
         <f>Y73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>27028452.031747244</v>
+        <v>28788512.258242548</v>
       </c>
       <c r="Z74">
         <f>Z73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>25142746.076043952</v>
+        <v>26780011.403016325</v>
       </c>
       <c r="AA74">
         <f>AA73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>23388601.000971116</v>
+        <v>24911638.51443379</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B78">
         <f>SUM(B74:AA74) / SUM(C76:AA76)</f>
-        <v>6.0852897778049826</v>
+        <v>6.4170040635192676</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="B79">
         <f>B78 * Inputs!$C$15</f>
-        <v>4.8864876915774014</v>
+        <v>5.1528542630059722</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.25">
@@ -25525,103 +25525,103 @@
       </c>
       <c r="C82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="D82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="E82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="F82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="G82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="H82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="I82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="J82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="K82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="L82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="M82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="N82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="O82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="P82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Q82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="R82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="S82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="T82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="U82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="V82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="W82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="X82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Y82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Z82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="AA82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.25">
@@ -25742,103 +25742,103 @@
       </c>
       <c r="C84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="D84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="E84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="F84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="G84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="H84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="I84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="J84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="K84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="L84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="M84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="N84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="O84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="P84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Q84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="R84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="S84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="T84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="U84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="V84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="W84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="X84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Y84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Z84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="AA84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
@@ -25851,103 +25851,103 @@
       </c>
       <c r="C85">
         <f>C84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>123895890.71063122</v>
+        <v>132535890.71063122</v>
       </c>
       <c r="D85">
         <f>D84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>115251991.35872672</v>
+        <v>123289200.6610523</v>
       </c>
       <c r="E85">
         <f>E84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>107211154.75230393</v>
+        <v>114687628.52190913</v>
       </c>
       <c r="F85">
         <f>F84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>99731306.746329233</v>
+        <v>106686166.06689221</v>
       </c>
       <c r="G85">
         <f>G84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>92773308.601236507</v>
+        <v>99242945.178504378</v>
       </c>
       <c r="H85">
         <f>H84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>86300752.187196761</v>
+        <v>92319018.770701766</v>
       </c>
       <c r="I85">
         <f>I84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>80279769.476462096</v>
+        <v>85878156.996001631</v>
       </c>
       <c r="J85">
         <f>J84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>74678855.32694149</v>
+        <v>79886657.670699194</v>
       </c>
       <c r="K85">
         <f>K84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>69468702.629713014</v>
+        <v>74313169.926231816</v>
       </c>
       <c r="L85">
         <f>L84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>64622048.957872577</v>
+        <v>69128530.163936585</v>
       </c>
       <c r="M85">
         <f>M84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>60113533.914300069</v>
+        <v>64305609.454824716</v>
       </c>
       <c r="N85">
         <f>N84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>55919566.431907043</v>
+        <v>59819171.585883461</v>
       </c>
       <c r="O85">
         <f>O84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>52018201.332006551</v>
+        <v>55645741.010124147</v>
       </c>
       <c r="P85">
         <f>P84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>48389024.494889818</v>
+        <v>51763480.009417817</v>
       </c>
       <c r="Q85">
         <f>Q84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>45013046.041757971</v>
+        <v>48152074.427365415</v>
       </c>
       <c r="R85">
         <f>R84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>41872600.969077185</v>
+        <v>44792627.374293409</v>
       </c>
       <c r="S85">
         <f>S84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>38951256.715420641</v>
+        <v>41667560.348179922</v>
       </c>
       <c r="T85">
         <f>T84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>36233727.177135482</v>
+        <v>38760521.254120857</v>
       </c>
       <c r="U85">
         <f>U84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>33705792.722916722</v>
+        <v>36056298.841042653</v>
       </c>
       <c r="V85">
         <f>V84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>31354225.788759746</v>
+        <v>33540743.107946657</v>
       </c>
       <c r="W85">
         <f>W84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>29166721.66396255</v>
+        <v>31200691.263206191</v>
       </c>
       <c r="X85">
         <f>X84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>27131834.106011678</v>
+        <v>29023898.849494133</v>
       </c>
       <c r="Y85">
         <f>Y84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>25238915.447452724</v>
+        <v>26998975.673948031</v>
       </c>
       <c r="Z85">
         <f>Z84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>23478060.88135137</v>
+        <v>25115326.208323751</v>
       </c>
       <c r="AA85">
         <f>AA84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>21840056.633815229</v>
+        <v>23363094.147277907</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.25">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="B89">
         <f>SUM(B85:AA85) / SUM(C87:AA87)</f>
-        <v>4.2197665238643163</v>
+        <v>4.4616415238643166</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.25">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="B90">
         <f>B89 * Inputs!$C$15</f>
-        <v>3.388472518663046</v>
+        <v>3.5826981436630465</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
@@ -26200,103 +26200,103 @@
       </c>
       <c r="C93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="D93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="E93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="F93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="G93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="H93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="I93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="J93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="K93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="L93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="M93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="N93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="O93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="P93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Q93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="R93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="S93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="T93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="U93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="V93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="W93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="X93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Y93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Z93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="AA93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
@@ -26417,103 +26417,103 @@
       </c>
       <c r="C95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="D95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="E95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="F95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="G95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="H95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="I95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="J95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="K95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="L95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="M95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="N95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="O95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="P95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Q95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="R95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="S95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="T95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="U95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="V95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="W95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="X95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Y95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Z95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="AA95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
@@ -26526,103 +26526,103 @@
       </c>
       <c r="C96">
         <f>C95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>71463429.985718146</v>
+        <v>80103429.985718116</v>
       </c>
       <c r="D96">
         <f>D95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>66477609.289040141</v>
+        <v>74514818.591365695</v>
       </c>
       <c r="E96">
         <f>E95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>61839636.547944322</v>
+        <v>69316110.317549482</v>
       </c>
       <c r="F96">
         <f>F95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>57525243.300413318</v>
+        <v>64480102.620976269</v>
       </c>
       <c r="G96">
         <f>G95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>53511854.232942618</v>
+        <v>59981490.810210481</v>
       </c>
       <c r="H96">
         <f>H95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>49778469.053900123</v>
+        <v>55796735.637405105</v>
       </c>
       <c r="I96">
         <f>I95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>46305552.608279176</v>
+        <v>51903940.127818696</v>
       </c>
       <c r="J96">
         <f>J95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>43074932.658864357</v>
+        <v>48282735.002622046</v>
       </c>
       <c r="K96">
         <f>K95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>40069704.798943587</v>
+        <v>44914172.095462367</v>
       </c>
       <c r="L96">
         <f>L95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>37274143.999017298</v>
+        <v>41780625.205081284</v>
       </c>
       <c r="M96">
         <f>M95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>34673622.324667245</v>
+        <v>38865697.865191884</v>
       </c>
       <c r="N96">
         <f>N95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>32254532.395039301</v>
+        <v>36154137.549015708</v>
       </c>
       <c r="O96">
         <f>O95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>30004216.181431908</v>
+        <v>33631755.859549493</v>
       </c>
       <c r="P96">
         <f>P95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>27910898.773425031</v>
+        <v>31285354.287953019</v>
       </c>
       <c r="Q96">
         <f>Q95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>25963626.765976775</v>
+        <v>29102655.151584204</v>
       </c>
       <c r="R96">
         <f>R95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>24152210.945094675</v>
+        <v>27072237.350310892</v>
       </c>
       <c r="S96">
         <f>S95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>22467172.972181093</v>
+        <v>25183476.604940366</v>
       </c>
       <c r="T96">
         <f>T95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>20899695.788075436</v>
+        <v>23426489.865060806</v>
       </c>
       <c r="U96">
         <f>U95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>19441577.477279477</v>
+        <v>21792083.5954054</v>
       </c>
       <c r="V96">
         <f>V95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>18085188.350957654</v>
+        <v>20271705.670144558</v>
       </c>
       <c r="W96">
         <f>W95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>16823431.024146654</v>
+        <v>18857400.623390287</v>
       </c>
       <c r="X96">
         <f>X95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>15649703.278275957</v>
+        <v>17541768.021758407</v>
       </c>
       <c r="Y96">
         <f>Y95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>14557863.514675308</v>
+        <v>16317923.741170611</v>
       </c>
       <c r="Z96">
         <f>Z95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>13542198.618302613</v>
+        <v>15179463.945274988</v>
       </c>
       <c r="AA96">
         <f>AA95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>12597394.063537315</v>
+        <v>14120431.576999988</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="B100">
         <f>SUM(B96:AA96) / SUM(C98:AA98)</f>
-        <v>1.9426649442718937</v>
+        <v>2.1109258138371101</v>
       </c>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.25">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="B101">
         <f>B100 * Inputs!$C$15</f>
-        <v>1.5599599502503307</v>
+        <v>1.6950734285111995</v>
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
@@ -26875,103 +26875,103 @@
       </c>
       <c r="C104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="D104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="E104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="F104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="G104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="H104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="I104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="J104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="K104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="L104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="M104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="N104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="O104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="P104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Q104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="R104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="S104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="T104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="U104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="V104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="W104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="X104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Y104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Z104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="AA104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
@@ -27092,103 +27092,103 @@
       </c>
       <c r="C106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="D106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="E106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="F106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="G106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="H106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="I106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="J106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="K106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="L106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="M106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="N106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="O106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="P106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Q106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="R106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="S106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="T106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="U106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="V106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="W106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="X106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Y106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Z106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="AA106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.25">
@@ -27201,103 +27201,103 @@
       </c>
       <c r="C107">
         <f>C106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>87839877.670138836</v>
+        <v>96479877.670138866</v>
       </c>
       <c r="D107">
         <f>D106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>81711514.11175707</v>
+        <v>89748723.414082676</v>
       </c>
       <c r="E107">
         <f>E106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>76010710.801634476</v>
+        <v>83487184.571239695</v>
       </c>
       <c r="F107">
         <f>F106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>70707637.95500882</v>
+        <v>77662497.275571808</v>
       </c>
       <c r="G107">
         <f>G106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>65774546.934891924</v>
+        <v>72244183.512159824</v>
       </c>
       <c r="H107">
         <f>H106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>61185625.055713423</v>
+        <v>67203891.63921845</v>
       </c>
       <c r="I107">
         <f>I106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>56916860.516942717</v>
+        <v>62515248.036482275</v>
       </c>
       <c r="J107">
         <f>J106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>52945916.759946719</v>
+        <v>58153719.103704445</v>
       </c>
       <c r="K107">
         <f>K106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>49252015.590648107</v>
+        <v>54096482.887166925</v>
       </c>
       <c r="L107">
         <f>L106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>45815828.456416853</v>
+        <v>50322309.662480868</v>
       </c>
       <c r="M107">
         <f>M106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>42619375.308294743</v>
+        <v>46811450.848819405</v>
       </c>
       <c r="N107">
         <f>N106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>39645930.51934395</v>
+        <v>43545535.673320383</v>
       </c>
       <c r="O107">
         <f>O106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>36879935.366831578</v>
+        <v>40507475.044949189</v>
       </c>
       <c r="P107">
         <f>P106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>34306916.620308444</v>
+        <v>37681372.134836458</v>
       </c>
       <c r="Q107">
         <f>Q106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>31913410.809589256</v>
+        <v>35052439.195196703</v>
       </c>
       <c r="R107">
         <f>R106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>29686893.776362099</v>
+        <v>32606920.181578334</v>
       </c>
       <c r="S107">
         <f>S106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>27615715.140801955</v>
+        <v>30332018.773561243</v>
       </c>
       <c r="T107">
         <f>T106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>25689037.34028089</v>
+        <v>28215831.417266276</v>
       </c>
       <c r="U107">
         <f>U106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>23896778.921191525</v>
+        <v>26247285.039317463</v>
       </c>
       <c r="V107">
         <f>V106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>22229561.787154905</v>
+        <v>24416079.106341828</v>
       </c>
       <c r="W107">
         <f>W106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>20678662.127585959</v>
+        <v>22712631.726829603</v>
       </c>
       <c r="X107">
         <f>X106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>19235964.769847404</v>
+        <v>21128029.513329867</v>
       </c>
       <c r="Y107">
         <f>Y106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>17893920.716137119</v>
+        <v>19653980.942632433</v>
       </c>
       <c r="Z107">
         <f>Z106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>16645507.642918253</v>
+        <v>18282772.969890639</v>
       </c>
       <c r="AA107">
         <f>AA106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>15484193.156203024</v>
+        <v>17007230.669665709</v>
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.25">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="B111">
         <f>SUM(B107:AA107) / SUM(C109:AA109)</f>
-        <v>2.3080417565764013</v>
+        <v>2.4787770506940499</v>
       </c>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.25">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="B112">
         <f>B111 * Inputs!$C$15</f>
-        <v>1.8533575305308503</v>
+        <v>1.9904579717073221</v>
       </c>
     </row>
   </sheetData>
@@ -27653,103 +27653,103 @@
       </c>
       <c r="C4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="D4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="E4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="F4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="G4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="H4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="I4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="J4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="K4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="L4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="M4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="N4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="O4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="P4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Q4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="R4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="S4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="T4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="U4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="V4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="W4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="X4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Y4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="Z4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
       <c r="AA4">
         <f>('Cost Components'!$B$43  + 'Cost Components'!$B$40 + 'Cost Components'!$B$41) * 10^6</f>
-        <v>536850856.00618696</v>
+        <v>556074856.00618696</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -27870,103 +27870,103 @@
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="T6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="V6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="W6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="X6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Y6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
       <c r="AA6">
         <f t="shared" si="0"/>
-        <v>480050856.00618696</v>
+        <v>499274856.00618696</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -27979,103 +27979,103 @@
       </c>
       <c r="C7">
         <f>C6/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>448645659.81886631</v>
+        <v>466612014.95905322</v>
       </c>
       <c r="D7">
         <f>D6/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>419295009.17651057</v>
+        <v>436085995.28883481</v>
       </c>
       <c r="E7">
         <f>E6/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>391864494.55748647</v>
+        <v>407557004.94283623</v>
       </c>
       <c r="F7">
         <f>F6/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>366228499.58643597</v>
+        <v>380894397.14283764</v>
       </c>
       <c r="G7">
         <f>G6/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>342269625.78171587</v>
+        <v>355976072.09610987</v>
       </c>
       <c r="H7">
         <f>H6/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>319878154.93618304</v>
+        <v>332687917.84683168</v>
       </c>
       <c r="I7">
         <f>I6/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>298951546.66932994</v>
+        <v>310923287.70731932</v>
       </c>
       <c r="J7">
         <f>J6/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>279393968.84984106</v>
+        <v>290582511.87599939</v>
       </c>
       <c r="K7">
         <f>K6/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>261115858.73816919</v>
+        <v>271572441.00560689</v>
       </c>
       <c r="L7">
         <f>L6/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>244033512.83941048</v>
+        <v>253806019.6314083</v>
       </c>
       <c r="M7">
         <f>M6/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>228068703.58823407</v>
+        <v>237201887.50598904</v>
       </c>
       <c r="N7">
         <f>N6/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>213148321.11049917</v>
+        <v>221684007.01494306</v>
       </c>
       <c r="O7">
         <f>O6/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>199204038.42102724</v>
+        <v>207181314.96723649</v>
       </c>
       <c r="P7">
         <f>P6/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>186171998.52432454</v>
+        <v>193627397.16564161</v>
       </c>
       <c r="Q7">
         <f>Q6/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>173992521.98535001</v>
+        <v>180960184.26695475</v>
       </c>
       <c r="R7">
         <f>R6/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>162609833.63116825</v>
+        <v>169121667.53921005</v>
       </c>
       <c r="S7">
         <f>S6/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>151971807.13193294</v>
+        <v>158057633.21421501</v>
       </c>
       <c r="T7">
         <f>T6/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>142029726.29152611</v>
+        <v>147717414.21889251</v>
       </c>
       <c r="U7">
         <f>U6/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>132738061.9546973</v>
+        <v>138053658.14849767</v>
       </c>
       <c r="V7">
         <f>V6/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>124054263.5090629</v>
+        <v>129022110.41915672</v>
       </c>
       <c r="W7">
         <f>W6/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>115938564.02716158</v>
+        <v>120581411.60668851</v>
       </c>
       <c r="X7">
         <f>X6/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>108353798.15622579</v>
+        <v>112692908.04363413</v>
       </c>
       <c r="Y7">
         <f>Y6/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>101265231.92170633</v>
+        <v>105320474.8071347</v>
       </c>
       <c r="Z7">
         <f>Z6/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>94640403.665146112</v>
+        <v>98430350.287041768</v>
       </c>
       <c r="AA7">
         <f>AA6/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>88448975.387987018</v>
+        <v>91990981.576674551</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -28300,7 +28300,7 @@
       </c>
       <c r="B11">
         <f>SUM(B7:AA7) / SUM(C9:AA9)</f>
-        <v>8.2988048787636615</v>
+        <v>8.5750117753153869</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -28309,7 +28309,7 @@
       </c>
       <c r="B12">
         <f>B11 * Inputs!$C$15</f>
-        <v>6.6639403176472207</v>
+        <v>6.8857344555782563</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -28327,103 +28327,103 @@
       </c>
       <c r="C15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="D15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="E15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="F15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="G15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="H15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="I15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="J15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="K15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="L15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="M15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="N15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="O15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="P15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Q15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="R15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="S15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="T15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="U15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="V15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="W15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="X15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Y15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="Z15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
       <c r="AA15">
         <f>('Cost Components'!$C$43  + 'Cost Components'!$C$40 + 'Cost Components'!$C$41) * 10^6</f>
-        <v>464027639.09935445</v>
+        <v>483251639.09935451</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -28544,103 +28544,103 @@
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="D17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="E17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="I17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="K17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="L17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="M17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="N17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="O17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Q17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="R17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="S17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="T17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="U17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="V17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="W17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="X17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Y17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="Z17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
       <c r="AA17">
         <f t="shared" si="1"/>
-        <v>314127639.09935451</v>
+        <v>333351639.09935451</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -28653,103 +28653,103 @@
       </c>
       <c r="C18">
         <f>C17/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>293577232.80313504</v>
+        <v>311543587.94332194</v>
       </c>
       <c r="D18">
         <f>D17/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>274371245.61040658</v>
+        <v>291162231.72273082</v>
       </c>
       <c r="E18">
         <f>E17/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>256421724.86953884</v>
+        <v>272114235.25488859</v>
       </c>
       <c r="F18">
         <f>F17/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>239646471.84069052</v>
+        <v>254312369.39709216</v>
       </c>
       <c r="G18">
         <f>G17/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>223968665.27167338</v>
+        <v>237675111.58606741</v>
       </c>
       <c r="H18">
         <f>H17/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>209316509.59969476</v>
+        <v>222126272.5103434</v>
       </c>
       <c r="I18">
         <f>I17/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>195622906.16793901</v>
+        <v>207594647.20592839</v>
       </c>
       <c r="J18">
         <f>J17/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>182825145.95134488</v>
+        <v>194013688.97750318</v>
       </c>
       <c r="K18">
         <f>K17/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>170864622.38443443</v>
+        <v>181321204.6518721</v>
       </c>
       <c r="L18">
         <f>L17/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>159686562.97610697</v>
+        <v>169459069.76810479</v>
       </c>
       <c r="M18">
         <f>M17/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>149239778.48234293</v>
+        <v>158372962.40009791</v>
       </c>
       <c r="N18">
         <f>N17/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>139476428.48817101</v>
+        <v>148012114.3926149</v>
       </c>
       <c r="O18">
         <f>O17/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>130351802.32539344</v>
+        <v>138329078.87160268</v>
       </c>
       <c r="P18">
         <f>P17/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>121824114.32279761</v>
+        <v>129279512.96411467</v>
       </c>
       <c r="Q18">
         <f>Q17/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>113854312.45121272</v>
+        <v>120821974.73281744</v>
       </c>
       <c r="R18">
         <f>R17/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>106405899.4871147</v>
+        <v>112917733.3951565</v>
       </c>
       <c r="S18">
         <f>S17/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>99444765.875808135</v>
+        <v>105530591.95809019</v>
       </c>
       <c r="T18">
         <f>T17/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>92939033.52879265</v>
+        <v>98626721.45615904</v>
       </c>
       <c r="U18">
         <f>U17/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>86858909.839993119</v>
+        <v>92174506.033793494</v>
       </c>
       <c r="V18">
         <f>V17/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>81176551.25233002</v>
+        <v>86144398.162423834</v>
       </c>
       <c r="W18">
         <f>W17/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>75865935.749841139</v>
+        <v>80508783.32936807</v>
       </c>
       <c r="X18">
         <f>X17/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>70902743.691440314</v>
+        <v>75241853.57884866</v>
       </c>
       <c r="Y18">
         <f>Y17/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>66264246.440598428</v>
+        <v>70319489.326026782</v>
       </c>
       <c r="Z18">
         <f>Z17/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>61929202.280933104</v>
+        <v>65719148.902828768</v>
       </c>
       <c r="AA18">
         <f>AA17/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>57877759.141058974</v>
+        <v>61419765.329746507</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="B22">
         <f>SUM(B18:AA18) / SUM(C20:AA20)</f>
-        <v>13.75423857128612</v>
+        <v>14.440809999857546</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="B23">
         <f>B22 * Inputs!$C$15</f>
-        <v>11.044653572742755</v>
+        <v>11.595970429885609</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
@@ -29001,103 +29001,103 @@
       </c>
       <c r="C26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="D26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="E26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="F26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="G26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="H26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="I26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="J26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="K26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="L26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="M26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="N26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="O26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="P26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Q26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="R26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="S26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="T26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="U26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="V26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="W26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="X26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Y26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="Z26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
       <c r="AA26">
         <f>('Cost Components'!$D$43  + 'Cost Components'!$D$40 + 'Cost Components'!$D$41) * 10^6</f>
-        <v>524956078.62649339</v>
+        <v>544180078.62649345</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
@@ -29218,103 +29218,103 @@
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="E28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="F28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="G28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="I28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="J28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="K28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="L28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="M28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="N28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="O28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="P28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Q28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="R28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="S28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="T28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="U28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="V28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="W28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="X28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Y28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="Z28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
       <c r="AA28">
         <f t="shared" si="2"/>
-        <v>443956078.62649339</v>
+        <v>463180078.62649345</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
@@ -29327,103 +29327,103 @@
       </c>
       <c r="C29">
         <f>C28/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>414912223.01541436</v>
+        <v>432878578.15560132</v>
       </c>
       <c r="D29">
         <f>D28/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>387768432.72468632</v>
+        <v>404559418.83701062</v>
       </c>
       <c r="E29">
         <f>E28/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>362400404.4155947</v>
+        <v>378092914.80094445</v>
       </c>
       <c r="F29">
         <f>F28/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>338691966.74354649</v>
+        <v>353357864.29994816</v>
       </c>
       <c r="G29">
         <f>G28/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>316534548.35845459</v>
+        <v>330240994.6728487</v>
       </c>
       <c r="H29">
         <f>H28/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>295826680.70883608</v>
+        <v>308636443.61948478</v>
       </c>
       <c r="I29">
         <f>I28/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>276473533.37274402</v>
+        <v>288445274.4107334</v>
       </c>
       <c r="J29">
         <f>J28/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>258386479.78761122</v>
+        <v>269575022.81376958</v>
       </c>
       <c r="K29">
         <f>K28/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>241482691.39029083</v>
+        <v>251939273.65772852</v>
       </c>
       <c r="L29">
         <f>L28/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>225684758.30868304</v>
+        <v>235457265.10068089</v>
       </c>
       <c r="M29">
         <f>M28/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>210920334.86792803</v>
+        <v>220053518.78568304</v>
       </c>
       <c r="N29">
         <f>N28/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>197121808.28778327</v>
+        <v>205657494.19222718</v>
       </c>
       <c r="O29">
         <f>O28/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>184225989.05400303</v>
+        <v>192203265.60021231</v>
       </c>
       <c r="P29">
         <f>P28/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>172173821.54579723</v>
+        <v>179629220.1871143</v>
       </c>
       <c r="Q29">
         <f>Q28/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>160910113.594203</v>
+        <v>167877775.87580773</v>
       </c>
       <c r="R29">
         <f>R28/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>150383283.73290002</v>
+        <v>156895117.64094183</v>
       </c>
       <c r="S29">
         <f>S28/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>140545124.98401871</v>
+        <v>146630951.06630078</v>
       </c>
       <c r="T29">
         <f>T28/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>131350584.09721375</v>
+        <v>137038272.02458018</v>
       </c>
       <c r="U29">
         <f>U28/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>122757555.23104088</v>
+        <v>128073151.42484127</v>
       </c>
       <c r="V29">
         <f>V28/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>114726687.13181391</v>
+        <v>119694534.04190774</v>
       </c>
       <c r="W29">
         <f>W28/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>107221202.92692888</v>
+        <v>111864050.50645582</v>
       </c>
       <c r="X29">
         <f>X28/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>100206731.70741017</v>
+        <v>104545841.59481853</v>
       </c>
       <c r="Y29">
         <f>Y28/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>93651151.128420725</v>
+        <v>97706394.013849095</v>
       </c>
       <c r="Z29">
         <f>Z28/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>87524440.306935251</v>
+        <v>91314386.928830922</v>
       </c>
       <c r="AA29">
         <f>AA28/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>81798542.342930138</v>
+        <v>85340548.531617671</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="B33">
         <f>SUM(B29:AA29) / SUM(C31:AA31)</f>
-        <v>13.543556815540116</v>
+        <v>14.044181815540117</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
@@ -29657,7 +29657,7 @@
       </c>
       <c r="B34">
         <f>B33 * Inputs!$C$15</f>
-        <v>10.875476122878714</v>
+        <v>11.277477997878714</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
@@ -29675,103 +29675,103 @@
       </c>
       <c r="C37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="D37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="E37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="F37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="G37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="H37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="I37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="J37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="K37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="L37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="M37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="N37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="O37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="P37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Q37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="R37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="S37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="T37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="U37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="V37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="W37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="X37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Y37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="Z37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
       <c r="AA37">
         <f>('Cost Components'!$E$43  + 'Cost Components'!$E$40 + 'Cost Components'!$E$41) * 10^6</f>
-        <v>469254180.27430987</v>
+        <v>488478180.27430993</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
@@ -29892,103 +29892,103 @@
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="D39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="E39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="F39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="G39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="H39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="I39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="J39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="K39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="L39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="M39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="N39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="O39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="P39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Q39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="R39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="S39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="T39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="U39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="V39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="W39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="X39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Y39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="Z39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
       <c r="AA39">
         <f t="shared" si="3"/>
-        <v>366054180.27430987</v>
+        <v>385278180.27430993</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
@@ -30001,103 +30001,103 @@
       </c>
       <c r="C40">
         <f>C39/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>342106710.53673816</v>
+        <v>360073065.67692512</v>
       </c>
       <c r="D40">
         <f>D39/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>319725897.69788617</v>
+        <v>336516883.81021041</v>
       </c>
       <c r="E40">
         <f>E39/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>298809250.18494034</v>
+        <v>314501760.57029009</v>
       </c>
       <c r="F40">
         <f>F39/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>279260981.48125267</v>
+        <v>293926879.03765434</v>
       </c>
       <c r="G40">
         <f>G39/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>260991571.47780618</v>
+        <v>274698017.79220027</v>
       </c>
       <c r="H40">
         <f>H39/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>243917356.5213142</v>
+        <v>256727119.43196291</v>
       </c>
       <c r="I40">
         <f>I39/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>227960146.28160205</v>
+        <v>239931887.31959146</v>
       </c>
       <c r="J40">
         <f>J39/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>213046865.68374026</v>
+        <v>224235408.70989859</v>
       </c>
       <c r="K40">
         <f>K39/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>199109220.26517779</v>
+        <v>209565802.53261548</v>
       </c>
       <c r="L40">
         <f>L39/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>186083383.42539981</v>
+        <v>195855890.21739766</v>
       </c>
       <c r="M40">
         <f>M39/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>173909704.13588765</v>
+        <v>183042888.05364263</v>
       </c>
       <c r="N40">
         <f>N39/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>162532433.77185765</v>
+        <v>171068119.67630157</v>
       </c>
       <c r="O40">
         <f>O39/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>151899470.8148202</v>
+        <v>159876747.36102948</v>
       </c>
       <c r="P40">
         <f>P39/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>141962122.25684133</v>
+        <v>149417520.8981584</v>
       </c>
       <c r="Q40">
         <f>Q39/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>132674880.61387038</v>
+        <v>139642542.89547512</v>
       </c>
       <c r="R40">
         <f>R39/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>123995215.52698168</v>
+        <v>130507049.4350235</v>
       </c>
       <c r="S40">
         <f>S39/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>115883378.99717915</v>
+        <v>121969205.07946122</v>
       </c>
       <c r="T40">
         <f>T39/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>108302223.36184967</v>
+        <v>113989911.28921609</v>
       </c>
       <c r="U40">
         <f>U39/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>101217031.17929874</v>
+        <v>106532627.37309913</v>
       </c>
       <c r="V40">
         <f>V39/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>94595356.24233529</v>
+        <v>99563203.152429104</v>
       </c>
       <c r="W40">
         <f>W39/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>88406874.992836714</v>
+        <v>93049722.572363645</v>
       </c>
       <c r="X40">
         <f>X39/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>82623247.656856745</v>
+        <v>86962357.544265091</v>
       </c>
       <c r="Y40">
         <f>Y39/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>77217988.464352086</v>
+        <v>81273231.349780455</v>
       </c>
       <c r="Z40">
         <f>Z39/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>72166344.359207556</v>
+        <v>75956290.981103227</v>
       </c>
       <c r="AA40">
         <f>AA39/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>67445181.644119203</v>
+        <v>70987187.832806751</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
@@ -30322,7 +30322,7 @@
       </c>
       <c r="B44">
         <f>SUM(B40:AA40) / SUM(C42:AA42)</f>
-        <v>7.9448768566013488</v>
+        <v>8.2931377261665684</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
@@ -30331,7 +30331,7 @@
       </c>
       <c r="B45">
         <f>B44 * Inputs!$C$15</f>
-        <v>6.3797361158508838</v>
+        <v>6.6593895941117545</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
@@ -30349,103 +30349,103 @@
       </c>
       <c r="C48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="D48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="E48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="F48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="G48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="H48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="I48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="J48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="K48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="L48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="M48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="N48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="O48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="P48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Q48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="R48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="S48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="T48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="U48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="V48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="W48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="X48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Y48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="Z48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
       <c r="AA48">
         <f>('Cost Components'!$F$43  + 'Cost Components'!$F$40 + 'Cost Components'!$F$41) * 10^6</f>
-        <v>509954143.97323191</v>
+        <v>529178143.97323197</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
@@ -30566,103 +30566,103 @@
       </c>
       <c r="C50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="D50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="E50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="F50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="G50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="H50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="I50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="J50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="K50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="L50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="M50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="N50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="O50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="P50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Q50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="R50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="S50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="T50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="U50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="V50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="W50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="X50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Y50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="Z50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
       <c r="AA50">
         <f t="shared" si="4"/>
-        <v>374754143.97323191</v>
+        <v>393978143.97323197</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
@@ -30675,103 +30675,103 @@
       </c>
       <c r="C51">
         <f>C50/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>350237517.73199242</v>
+        <v>368203872.87217939</v>
       </c>
       <c r="D51">
         <f>D50/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>327324782.92709571</v>
+        <v>344115769.03942001</v>
       </c>
       <c r="E51">
         <f>E50/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>305911012.08139783</v>
+        <v>321603522.46674764</v>
       </c>
       <c r="F51">
         <f>F50/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>285898142.13214755</v>
+        <v>300564039.68854922</v>
       </c>
       <c r="G51">
         <f>G50/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>267194525.35714722</v>
+        <v>280900971.67154127</v>
       </c>
       <c r="H51">
         <f>H50/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>249714509.67957687</v>
+        <v>262524272.59022555</v>
       </c>
       <c r="I51">
         <f>I50/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>233378046.42951107</v>
+        <v>245349787.46750048</v>
       </c>
       <c r="J51">
         <f>J50/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>218110323.7658982</v>
+        <v>229298866.79205653</v>
       </c>
       <c r="K51">
         <f>K50/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>203841424.08027866</v>
+        <v>214298006.34771636</v>
       </c>
       <c r="L51">
         <f>L50/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>190506003.81334457</v>
+        <v>200278510.60534242</v>
       </c>
       <c r="M51">
         <f>M50/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>178042994.218079</v>
+        <v>187176178.13583401</v>
       </c>
       <c r="N51">
         <f>N50/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>166395321.6991393</v>
+        <v>174931007.60358322</v>
       </c>
       <c r="O51">
         <f>O50/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>155509646.44779372</v>
+        <v>163486922.994003</v>
       </c>
       <c r="P51">
         <f>P50/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>145336118.17550814</v>
+        <v>152791516.81682524</v>
       </c>
       <c r="Q51">
         <f>Q50/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>135828147.82757771</v>
+        <v>142795810.10918245</v>
       </c>
       <c r="R51">
         <f>R50/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>126942194.23138104</v>
+        <v>133454028.13942286</v>
       </c>
       <c r="S51">
         <f>S50/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>118637564.70222527</v>
+        <v>124723390.78450735</v>
       </c>
       <c r="T51">
         <f>T50/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>110876228.69366847</v>
+        <v>116563916.62103491</v>
       </c>
       <c r="U51">
         <f>U50/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>103622643.63894249</v>
+        <v>108938239.83274288</v>
       </c>
       <c r="V51">
         <f>V50/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>96843592.18592757</v>
+        <v>101811439.0960214</v>
       </c>
       <c r="W51">
         <f>W50/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>90508030.080306143</v>
+        <v>95150877.659833074</v>
       </c>
       <c r="X51">
         <f>X50/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>84586944.000286117</v>
+        <v>88926053.887694463</v>
       </c>
       <c r="Y51">
         <f>Y50/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>79053218.691856176</v>
+        <v>83108461.577284545</v>
       </c>
       <c r="Z51">
         <f>Z50/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>73881512.79612726</v>
+        <v>77671459.418022946</v>
       </c>
       <c r="AA51">
         <f>AA50/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>69048142.800118938</v>
+        <v>72590148.988806486</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="B55">
         <f>SUM(B51:AA51) / SUM(C53:AA53)</f>
-        <v>8.383701079458973</v>
+        <v>8.7370834324001478</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
@@ -31005,7 +31005,7 @@
       </c>
       <c r="B56">
         <f>B55 * Inputs!$C$15</f>
-        <v>6.7321119668055553</v>
+        <v>7.015877996217319</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
@@ -31028,103 +31028,103 @@
       </c>
       <c r="C60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="D60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="E60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="F60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="G60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="H60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="I60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="J60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="K60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="L60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="M60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="N60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="O60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="P60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Q60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="R60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="S60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="T60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="U60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="V60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="W60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="X60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Y60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="Z60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
       <c r="AA60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>259413747.37606338</v>
+        <v>268701747.37606341</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
@@ -31245,103 +31245,103 @@
       </c>
       <c r="C62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="D62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="E62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="F62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="G62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="H62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="I62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="J62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="K62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="L62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="M62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="N62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="O62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="P62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Q62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="R62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="S62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="T62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="U62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="V62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="W62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="X62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Y62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="Z62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
       <c r="AA62">
         <f t="shared" si="5"/>
-        <v>109513747.37606338</v>
+        <v>118801747.37606341</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -31354,103 +31354,103 @@
       </c>
       <c r="C63">
         <f>C62/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>102349296.61314334</v>
+        <v>111029670.44491906</v>
       </c>
       <c r="D63">
         <f>D62/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>95653548.236582562</v>
+        <v>103766047.14478418</v>
       </c>
       <c r="E63">
         <f>E62/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>89395839.473441646</v>
+        <v>96977614.154003903</v>
       </c>
       <c r="F63">
         <f>F62/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>83547513.526580974</v>
+        <v>90633284.256078422</v>
       </c>
       <c r="G63">
         <f>G62/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>78081788.342599034</v>
+        <v>84704003.977643371</v>
       </c>
       <c r="H63">
         <f>H62/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>72973633.96504584</v>
+        <v>79162620.539853618</v>
       </c>
       <c r="I63">
         <f>I62/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>68199657.911257789</v>
+        <v>73983757.513881892</v>
       </c>
       <c r="J63">
         <f>J62/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>63737998.047904477</v>
+        <v>69143698.611104563</v>
       </c>
       <c r="K63">
         <f>K62/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>59568222.474677071</v>
+        <v>64620279.075798653</v>
       </c>
       <c r="L63">
         <f>L62/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>55671235.957642123</v>
+        <v>60392784.182989404</v>
       </c>
       <c r="M63">
         <f>M62/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>52029192.48377768</v>
+        <v>56441854.376625597</v>
       </c>
       <c r="N63">
         <f>N62/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>48625413.536240831</v>
+        <v>52749396.613668792</v>
       </c>
       <c r="O63">
         <f>O62/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>45444311.716112927</v>
+        <v>49298501.508101672</v>
       </c>
       <c r="P63">
         <f>P62/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>42471319.360853203</v>
+        <v>46073365.895422131</v>
       </c>
       <c r="Q63">
         <f>Q62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>39692821.832573079</v>
+        <v>43059220.463011332</v>
       </c>
       <c r="R63">
         <f>R62/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>37096095.170629054</v>
+        <v>40242262.114963867</v>
       </c>
       <c r="S63">
         <f>S62/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>34669247.823017806</v>
+        <v>37609590.761648469</v>
       </c>
       <c r="T63">
         <f>T62/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>32401166.189736266</v>
+        <v>35149150.244531281</v>
       </c>
       <c r="U63">
         <f>U62/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>30281463.728725482</v>
+        <v>32849673.125730168</v>
       </c>
       <c r="V63">
         <f>V62/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>28300433.391332228</v>
+        <v>30700629.089467447</v>
       </c>
       <c r="W63">
         <f>W62/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>26449003.169469371</v>
+        <v>28692176.719128456</v>
       </c>
       <c r="X63">
         <f>X62/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>24718694.550905954</v>
+        <v>26815118.429092012</v>
       </c>
       <c r="Y63">
         <f>Y62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>23101583.692435469</v>
+        <v>25060858.344945807</v>
       </c>
       <c r="Z63">
         <f>Z62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>21590265.133117262</v>
+        <v>23421362.939201687</v>
       </c>
       <c r="AA63">
         <f>AA62/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>20177817.881418001</v>
+        <v>21889124.242244568</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -31676,7 +31676,7 @@
       </c>
       <c r="B67">
         <f>SUM(B63:AA63) / SUM(C65:AA65)</f>
-        <v>2.1014053283039136</v>
+        <v>2.2348536041659832</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
@@ -31685,7 +31685,7 @@
       </c>
       <c r="B68">
         <f>B67 * Inputs!$C$15</f>
-        <v>1.6874284786280427</v>
+        <v>1.7945874441452847</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
@@ -31703,103 +31703,103 @@
       </c>
       <c r="C71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="D71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="E71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="F71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="G71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="H71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="I71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="J71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="K71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="L71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="M71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="N71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="O71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="P71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Q71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="R71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="S71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="T71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="U71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="V71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="W71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="X71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Y71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="Z71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
       <c r="AA71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>223631631.97020158</v>
+        <v>232919631.97020155</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
@@ -31920,103 +31920,103 @@
       </c>
       <c r="C73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="D73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="G73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="H73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="I73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="J73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="K73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="L73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="M73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="N73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="O73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="P73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Q73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="R73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="S73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="T73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="U73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="V73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="W73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="X73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Y73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="Z73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
       <c r="AA73">
         <f t="shared" si="6"/>
-        <v>142631631.97020158</v>
+        <v>151919631.97020155</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
@@ -32029,103 +32029,103 @@
       </c>
       <c r="C74">
         <f>C73/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>133300590.62635662</v>
+        <v>141980964.4581323</v>
       </c>
       <c r="D74">
         <f>D73/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>124579991.23958562</v>
+        <v>132692490.14778718</v>
       </c>
       <c r="E74">
         <f>E73/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>116429898.35475291</v>
+        <v>124011673.03531513</v>
       </c>
       <c r="F74">
         <f>F73/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>108812989.11659151</v>
+        <v>115898759.8460889</v>
       </c>
       <c r="G74">
         <f>G73/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>101694382.35195467</v>
+        <v>108316597.98699896</v>
       </c>
       <c r="H74">
         <f>H73/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>95041478.833602503</v>
+        <v>101230465.40841025</v>
       </c>
       <c r="I74">
         <f>I73/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>88823811.994021028</v>
+        <v>94607911.596645087</v>
       </c>
       <c r="J74">
         <f>J73/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>83012908.405627131</v>
+        <v>88418608.968827188</v>
       </c>
       <c r="K74">
         <f>K73/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>77582157.388436556</v>
+        <v>82634213.989558116</v>
       </c>
       <c r="L74">
         <f>L73/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>72506689.148071557</v>
+        <v>77228237.373418808</v>
       </c>
       <c r="M74">
         <f>M73/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>67763260.886048183</v>
+        <v>72175922.778896064</v>
       </c>
       <c r="N74">
         <f>N73/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>63330150.360792704</v>
+        <v>67454133.438220635</v>
       </c>
       <c r="O74">
         <f>O73/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>59187056.411955789</v>
+        <v>63041246.203944512</v>
       </c>
       <c r="P74">
         <f>P73/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>55315005.992482051</v>
+        <v>58917052.52705095</v>
       </c>
       <c r="Q74">
         <f>Q73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>51696267.282693498</v>
+        <v>55062665.913131721</v>
       </c>
       <c r="R74">
         <f>R73/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>48314268.488498606</v>
+        <v>51460435.432833396</v>
       </c>
       <c r="S74">
         <f>S73/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>45153521.951867856</v>
+        <v>48093864.890498497</v>
       </c>
       <c r="T74">
         <f>T73/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>42199553.226044722</v>
+        <v>44947537.280839719</v>
       </c>
       <c r="U74">
         <f>U73/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>39438834.790696003</v>
+        <v>42007044.187700666</v>
       </c>
       <c r="V74">
         <f>V73/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>36858724.10345421</v>
+        <v>39258919.801589414</v>
       </c>
       <c r="W74">
         <f>W73/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>34447405.704162806</v>
+        <v>36690579.25382188</v>
       </c>
       <c r="X74">
         <f>X73/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>32193837.106694214</v>
+        <v>34290260.984880261</v>
       </c>
       <c r="Y74">
         <f>Y73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>30087698.230555341</v>
+        <v>32046972.883065663</v>
       </c>
       <c r="Z74">
         <f>Z73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>28119344.140705924</v>
+        <v>29950441.946790338</v>
       </c>
       <c r="AA74">
         <f>AA73/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>26279760.879164413</v>
+        <v>27991067.239990968</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
@@ -32351,7 +32351,7 @@
       </c>
       <c r="B78">
         <f>SUM(B74:AA74) / SUM(C76:AA76)</f>
-        <v>6.0421930713669818</v>
+        <v>6.3739073570812694</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="B79">
         <f>B78 * Inputs!$C$15</f>
-        <v>4.8518810363076863</v>
+        <v>5.1182476077362598</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.25">
@@ -32378,103 +32378,103 @@
       </c>
       <c r="C82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="D82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="E82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="F82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="G82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="H82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="I82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="J82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="K82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="L82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="M82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="N82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="O82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="P82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Q82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="R82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="S82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="T82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="U82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="V82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="W82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="X82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Y82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="Z82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
       <c r="AA82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>236388082.51392856</v>
+        <v>245676082.51392856</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.25">
@@ -32595,103 +32595,103 @@
       </c>
       <c r="C84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="D84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="E84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="F84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="G84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="H84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="I84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="J84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="K84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="L84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="M84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="N84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="O84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="P84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Q84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="R84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="S84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="T84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="U84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="V84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="W84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="X84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Y84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="Z84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
       <c r="AA84">
         <f t="shared" si="7"/>
-        <v>133188082.51392856</v>
+        <v>142476082.51392856</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
@@ -32704,103 +32704,103 @@
       </c>
       <c r="C85">
         <f>C84/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>124474843.47096127</v>
+        <v>133155217.30273697</v>
       </c>
       <c r="D85">
         <f>D84/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>116331629.41211334</v>
+        <v>124444128.32031493</v>
       </c>
       <c r="E85">
         <f>E84/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>108721148.98328349</v>
+        <v>116302923.66384572</v>
       </c>
       <c r="F85">
         <f>F84/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>101608550.45166682</v>
+        <v>108694321.18116423</v>
       </c>
       <c r="G85">
         <f>G84/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>94961262.104361504</v>
+        <v>101583477.73940581</v>
       </c>
       <c r="H85">
         <f>H84/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>88748843.08818832</v>
+        <v>94937829.662996098</v>
       </c>
       <c r="I85">
         <f>I84/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>82942844.00765264</v>
+        <v>88726943.610276714</v>
       </c>
       <c r="J85">
         <f>J84/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>77516676.642666012</v>
+        <v>82922377.205866098</v>
       </c>
       <c r="K85">
         <f>K84/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>72445492.189407483</v>
+        <v>77497548.790529057</v>
       </c>
       <c r="L85">
         <f>L84/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>67706067.466735974</v>
+        <v>72427615.692083225</v>
       </c>
       <c r="M85">
         <f>M84/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>63276698.567042954</v>
+        <v>67689360.459890857</v>
       </c>
       <c r="N85">
         <f>N84/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>59137101.464526139</v>
+        <v>63261084.541954085</v>
       </c>
       <c r="O85">
         <f>O84/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>55268319.125725359</v>
+        <v>59122508.917714097</v>
       </c>
       <c r="P85">
         <f>P84/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>51652634.696939588</v>
+        <v>55254681.231508501</v>
       </c>
       <c r="Q85">
         <f>Q84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>48273490.370971575</v>
+        <v>51639889.001409806</v>
       </c>
       <c r="R85">
         <f>R84/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>45115411.561655678</v>
+        <v>48261578.505990483</v>
       </c>
       <c r="S85">
         <f>S84/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>42163936.038930543</v>
+        <v>45104278.977561198</v>
       </c>
       <c r="T85">
         <f>T84/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>39405547.699935086</v>
+        <v>42153531.75473009</v>
       </c>
       <c r="U85">
         <f>U84/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>36827614.672836527</v>
+        <v>39395824.069841206</v>
       </c>
       <c r="V85">
         <f>V84/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>34418331.469940685</v>
+        <v>36818527.168075897</v>
       </c>
       <c r="W85">
         <f>W84/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>32166664.925178204</v>
+        <v>34409838.474837281</v>
       </c>
       <c r="X85">
         <f>X84/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>30062303.668390848</v>
+        <v>32158727.546576899</v>
       </c>
       <c r="Y85">
         <f>Y84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>28095610.905038174</v>
+        <v>30054885.557548504</v>
       </c>
       <c r="Z85">
         <f>Z84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>26257580.285082404</v>
+        <v>28088678.091166824</v>
       </c>
       <c r="AA85">
         <f>AA84/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>24539794.658955518</v>
+        <v>26251101.019782078</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.25">
@@ -33026,7 +33026,7 @@
       </c>
       <c r="B89">
         <f>SUM(B85:AA85) / SUM(C87:AA87)</f>
-        <v>4.1871027305233</v>
+        <v>4.4289777305232976</v>
       </c>
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.25">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="B90">
         <f>B89 * Inputs!$C$15</f>
-        <v>3.3622434926102103</v>
+        <v>3.5564691176102081</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
@@ -33053,103 +33053,103 @@
       </c>
       <c r="C93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="D93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="E93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="F93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="G93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="H93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="I93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="J93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="K93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="L93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="M93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="N93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="O93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="P93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Q93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="R93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="S93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="T93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="U93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="V93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="W93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="X93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Y93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="Z93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
       <c r="AA93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>212023187.23464701</v>
+        <v>221311187.23464698</v>
       </c>
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
@@ -33270,103 +33270,103 @@
       </c>
       <c r="C95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="D95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="E95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="F95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="G95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="H95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="I95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="J95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="K95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="L95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="M95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="N95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="O95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="P95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Q95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="R95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="S95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="T95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="U95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="V95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="W95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="X95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Y95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="Z95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
       <c r="AA95">
         <f t="shared" si="8"/>
-        <v>76823187.234647006</v>
+        <v>86111187.234646976</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
@@ -33379,103 +33379,103 @@
       </c>
       <c r="C96">
         <f>C95/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>71797371.247333646</v>
+        <v>80477745.079109326</v>
       </c>
       <c r="D96">
         <f>D95/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>67100346.960124902</v>
+        <v>75212845.86832647</v>
       </c>
       <c r="E96">
         <f>E95/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>62710604.635630749</v>
+        <v>70292379.316192955</v>
       </c>
       <c r="F96">
         <f>F95/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>58608041.715542763</v>
+        <v>65693812.445040151</v>
       </c>
       <c r="G96">
         <f>G95/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>54773870.762189493</v>
+        <v>61396086.397233777</v>
       </c>
       <c r="H96">
         <f>H95/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>51190533.422607005</v>
+        <v>57379519.997414753</v>
       </c>
       <c r="I96">
         <f>I95/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>47841620.021128036</v>
+        <v>53625719.623752102</v>
       </c>
       <c r="J96">
         <f>J95/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>44711794.412269197</v>
+        <v>50117494.975469254</v>
       </c>
       <c r="K96">
         <f>K95/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>41786723.749784291</v>
+        <v>46838780.350905843</v>
       </c>
       <c r="L96">
         <f>L95/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>39053012.850265697</v>
+        <v>43774561.07561294</v>
       </c>
       <c r="M96">
         <f>M95/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>36498142.8507156</v>
+        <v>40910804.743563488</v>
       </c>
       <c r="N96">
         <f>N95/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>34110413.879173465</v>
+        <v>38234396.956601396</v>
       </c>
       <c r="O96">
         <f>O95/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>31878891.475863047</v>
+        <v>35733081.26785177</v>
       </c>
       <c r="P96">
         <f>P95/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>29793356.519498177</v>
+        <v>33395403.054067079</v>
       </c>
       <c r="Q96">
         <f>Q95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>27844258.429437544</v>
+        <v>31210657.059875768</v>
       </c>
       <c r="R96">
         <f>R95/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>26022671.429380886</v>
+        <v>29168838.373715676</v>
       </c>
       <c r="S96">
         <f>S95/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>24320253.672318585</v>
+        <v>27260596.610949229</v>
       </c>
       <c r="T96">
         <f>T95/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>22729209.039550077</v>
+        <v>25477193.094345074</v>
       </c>
       <c r="U96">
         <f>U95/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>21242251.438831847</v>
+        <v>23810460.835836515</v>
       </c>
       <c r="V96">
         <f>V95/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>19852571.438160606</v>
+        <v>22252767.13629581</v>
       </c>
       <c r="W96">
         <f>W95/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>18553805.082393087</v>
+        <v>20796978.632052157</v>
       </c>
       <c r="X96">
         <f>X95/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>17340004.749900084</v>
+        <v>19436428.628086131</v>
       </c>
       <c r="Y96">
         <f>Y95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>16205611.915794471</v>
+        <v>18164886.568304796</v>
       </c>
       <c r="Z96">
         <f>Z95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>15145431.697004177</v>
+        <v>16976529.503088593</v>
       </c>
       <c r="AA96">
         <f>AA95/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>14154609.062620725</v>
+        <v>15865915.423447281</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
@@ -33701,7 +33701,7 @@
       </c>
       <c r="B100">
         <f>SUM(B96:AA96) / SUM(C98:AA98)</f>
-        <v>1.9187129089212438</v>
+        <v>2.0869737784864602</v>
       </c>
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.25">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="B101">
         <f>B100 * Inputs!$C$15</f>
-        <v>1.5407264658637589</v>
+        <v>1.6758399441246277</v>
       </c>
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.25">
@@ -33728,103 +33728,103 @@
       </c>
       <c r="C104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="D104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="E104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="F104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="G104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="H104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="I104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="J104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="K104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="L104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="M104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="N104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="O104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="P104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Q104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="R104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="S104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="T104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="U104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="V104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="W104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="X104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Y104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="Z104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
       <c r="AA104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>228127868.49539924</v>
+        <v>237415868.49539927</v>
       </c>
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.25">
@@ -33945,103 +33945,103 @@
       </c>
       <c r="C106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="D106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="E106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="F106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="G106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="H106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="I106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="J106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="K106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="L106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="M106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="N106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="O106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="P106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Q106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="R106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="S106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="T106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="U106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="V106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="W106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="X106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Y106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="Z106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
       <c r="AA106">
         <f t="shared" si="9"/>
-        <v>94427868.495399252</v>
+        <v>103715868.49539928</v>
       </c>
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.25">
@@ -34054,103 +34054,103 @@
       </c>
       <c r="C107">
         <f>C106/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>88250344.388223588</v>
+        <v>96930718.219999328</v>
       </c>
       <c r="D107">
         <f>D106/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>82476957.372171581</v>
+        <v>90589456.280373201</v>
       </c>
       <c r="E107">
         <f>E106/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>77081268.572122976</v>
+        <v>84663043.252685234</v>
       </c>
       <c r="F107">
         <f>F106/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>72038568.758993432</v>
+        <v>79124339.48849088</v>
       </c>
       <c r="G107">
         <f>G106/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>67325765.195320964</v>
+        <v>73947980.8303653</v>
       </c>
       <c r="H107">
         <f>H106/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>62921275.883477539</v>
+        <v>69110262.458285332</v>
       </c>
       <c r="I107">
         <f>I106/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>58804930.732221998</v>
+        <v>64589030.334846094</v>
       </c>
       <c r="J107">
         <f>J106/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>54957879.188992523</v>
+        <v>60363579.752192616</v>
       </c>
       <c r="K107">
         <f>K106/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>51362503.914946273</v>
+        <v>56414560.516067863</v>
       </c>
       <c r="L107">
         <f>L106/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>48002340.107426427</v>
+        <v>52723888.3327737</v>
       </c>
       <c r="M107">
         <f>M106/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>44862000.100398526</v>
+        <v>49274661.993246444</v>
       </c>
       <c r="N107">
         <f>N106/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>41927102.897568725</v>
+        <v>46051085.974996686</v>
       </c>
       <c r="O107">
         <f>O106/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>39184208.315484785</v>
+        <v>43038398.107473537</v>
       </c>
       <c r="P107">
         <f>P106/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>36620755.435032509</v>
+        <v>40222801.969601437</v>
       </c>
       <c r="Q107">
         <f>Q106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>34225005.079469636</v>
+        <v>37591403.709907882</v>
       </c>
       <c r="R107">
         <f>R106/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>31985986.0555791</v>
+        <v>35132152.999913909</v>
       </c>
       <c r="S107">
         <f>S106/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>29893444.911756169</v>
+        <v>32833787.850386832</v>
       </c>
       <c r="T107">
         <f>T106/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>27937798.982949689</v>
+        <v>30685783.037744705</v>
       </c>
       <c r="U107">
         <f>U106/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>26110092.507429615</v>
+        <v>28678301.904434301</v>
       </c>
       <c r="V107">
         <f>V106/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>24401955.614420202</v>
+        <v>26802151.312555421</v>
       </c>
       <c r="W107">
         <f>W106/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>22805565.994785234</v>
+        <v>25048739.544444319</v>
       </c>
       <c r="X107">
         <f>X106/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>21313613.079238538</v>
+        <v>23410036.957424596</v>
       </c>
       <c r="Y107">
         <f>Y106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>19919264.560036015</v>
+        <v>21878539.212546352</v>
       </c>
       <c r="Z107">
         <f>Z106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>18616135.102837399</v>
+        <v>20447232.908921823</v>
       </c>
       <c r="AA107">
         <f>AA106/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>17398257.10545551</v>
+        <v>19109563.466282077</v>
       </c>
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.25">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="B111">
         <f>SUM(B107:AA107) / SUM(C109:AA109)</f>
-        <v>2.2831639332898943</v>
+        <v>2.4538992274075415</v>
       </c>
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.25">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="B112">
         <f>B111 * Inputs!$C$15</f>
-        <v>1.8333806384317852</v>
+        <v>1.9704810796082559</v>
       </c>
     </row>
   </sheetData>
@@ -34495,103 +34495,103 @@
       </c>
       <c r="C3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!C1</f>
-        <v>258.79626168224297</v>
+        <v>276.76261682242989</v>
       </c>
       <c r="D3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!D1</f>
-        <v>241.86566512359155</v>
+        <v>258.65665123591583</v>
       </c>
       <c r="E3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!E1</f>
-        <v>226.04267768559956</v>
+        <v>241.73518807094933</v>
       </c>
       <c r="F3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!F1</f>
-        <v>211.25483895850428</v>
+        <v>225.92073651490594</v>
       </c>
       <c r="G3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!G1</f>
-        <v>197.43442893318155</v>
+        <v>211.14087524757562</v>
       </c>
       <c r="H3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!H1</f>
-        <v>184.51815788147812</v>
+        <v>197.32792079212678</v>
       </c>
       <c r="I3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!I1</f>
-        <v>172.44687652474587</v>
+        <v>184.41861756273528</v>
       </c>
       <c r="J3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!J1</f>
-        <v>161.16530516331392</v>
+        <v>172.35384818947225</v>
       </c>
       <c r="K3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!K1</f>
-        <v>150.62178052646158</v>
+        <v>161.07836279389926</v>
       </c>
       <c r="L3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!L1</f>
-        <v>140.76801918360897</v>
+        <v>150.54052597560681</v>
       </c>
       <c r="M3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!M1</f>
-        <v>131.55889643327939</v>
+        <v>140.69208035103438</v>
       </c>
       <c r="N3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!N1</f>
-        <v>122.95223965727048</v>
+        <v>131.48792556171441</v>
       </c>
       <c r="O3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!O1</f>
-        <v>114.90863519371072</v>
+        <v>122.88591173991999</v>
       </c>
       <c r="P3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!P1</f>
-        <v>107.39124784458946</v>
+        <v>114.84664648590653</v>
       </c>
       <c r="Q3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!Q1</f>
-        <v>100.36565219120509</v>
+        <v>107.33331447280983</v>
       </c>
       <c r="R3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!R1</f>
-        <v>93.799674945051507</v>
+        <v>100.31150885309331</v>
       </c>
       <c r="S3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!S1</f>
-        <v>87.663247612197665</v>
+        <v>93.749073694479733</v>
       </c>
       <c r="T3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!T1</f>
-        <v>81.928268796446417</v>
+        <v>87.615956723812829</v>
       </c>
       <c r="U3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!U1</f>
-        <v>76.568475510697581</v>
+        <v>81.88407170449797</v>
       </c>
       <c r="V3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!V1</f>
-        <v>71.559322907194002</v>
+        <v>76.527169817287827</v>
       </c>
       <c r="W3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!W1</f>
-        <v>66.877871875882249</v>
+        <v>71.520719455409179</v>
       </c>
       <c r="X3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!X1</f>
-        <v>62.502683996151632</v>
+        <v>66.841793883559987</v>
       </c>
       <c r="Y3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!Y1</f>
-        <v>58.413723360889371</v>
+        <v>62.468966246317741</v>
       </c>
       <c r="Z3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!Z1</f>
-        <v>54.59226482326109</v>
+        <v>58.382211445156763</v>
       </c>
       <c r="AA3">
         <f>('Cost Components'!$B$41) / (1+Inputs!$C$5)^'Cost Breakdown'!AA1</f>
-        <v>51.020808246038399</v>
+        <v>54.562814434725944</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="B9" s="17">
         <f>SUM(B3:AA3) / SUM($B$3:$AA$6)</f>
-        <v>0.39002693268037147</v>
+        <v>0.40610761007463636</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
@@ -34914,7 +34914,7 @@
       </c>
       <c r="B10" s="17">
         <f t="shared" ref="B10:B12" si="0">SUM(B4:AA4) / SUM($B$3:$AA$6)</f>
-        <v>0.20146835912565156</v>
+        <v>0.19615706283762402</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="B11" s="17">
         <f t="shared" si="0"/>
-        <v>0.22610565079629083</v>
+        <v>0.22014484330776898</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
@@ -34932,7 +34932,7 @@
       </c>
       <c r="B12" s="17">
         <f t="shared" si="0"/>
-        <v>0.18239905739768625</v>
+        <v>0.17759048377997066</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
@@ -34949,103 +34949,103 @@
       </c>
       <c r="C15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!C1</f>
-        <v>96.89719626168224</v>
+        <v>105.57757009345794</v>
       </c>
       <c r="D15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!D1</f>
-        <v>90.558127347366579</v>
+        <v>98.670626255568166</v>
       </c>
       <c r="E15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!E1</f>
-        <v>84.633763876043531</v>
+        <v>92.215538556605765</v>
       </c>
       <c r="F15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!F1</f>
-        <v>79.096975585087421</v>
+        <v>86.182746314584833</v>
       </c>
       <c r="G15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!G1</f>
-        <v>73.922407088866734</v>
+        <v>80.544622723911047</v>
       </c>
       <c r="H15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!H1</f>
-        <v>69.086361765296019</v>
+        <v>75.27534834010379</v>
       </c>
       <c r="I15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!I1</f>
-        <v>64.566693238594411</v>
+        <v>70.350792841218492</v>
       </c>
       <c r="J15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!J1</f>
-        <v>60.342703961303187</v>
+        <v>65.748404524503258</v>
       </c>
       <c r="K15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!K1</f>
-        <v>56.395050431124467</v>
+        <v>61.447107032246031</v>
       </c>
       <c r="L15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!L1</f>
-        <v>52.705654608527546</v>
+        <v>57.427202833874802</v>
       </c>
       <c r="M15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!M1</f>
-        <v>49.257621129464987</v>
+        <v>53.670283022312894</v>
       </c>
       <c r="N15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!N1</f>
-        <v>46.035159934079438</v>
+        <v>50.159143011507382</v>
       </c>
       <c r="O15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!O1</f>
-        <v>43.02351395708358</v>
+        <v>46.877703749072317</v>
       </c>
       <c r="P15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!P1</f>
-        <v>40.208891548676249</v>
+        <v>43.810938083245162</v>
       </c>
       <c r="Q15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Q1</f>
-        <v>37.578403316519854</v>
+        <v>40.944801946958087</v>
       </c>
       <c r="R15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!R1</f>
-        <v>35.120003099551269</v>
+        <v>38.266170043886071</v>
       </c>
       <c r="S15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!S1</f>
-        <v>32.822432803318947</v>
+        <v>35.762775741949596</v>
       </c>
       <c r="T15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!T1</f>
-        <v>30.67517084422331</v>
+        <v>33.423154899018314</v>
       </c>
       <c r="U15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!U1</f>
-        <v>28.668383966563841</v>
+        <v>31.236593363568517</v>
       </c>
       <c r="V15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!V1</f>
-        <v>26.792882211741908</v>
+        <v>29.193077909877122</v>
       </c>
       <c r="W15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!W1</f>
-        <v>25.040076833403653</v>
+        <v>27.283250383062729</v>
       </c>
       <c r="X15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!X1</f>
-        <v>23.401940965797806</v>
+        <v>25.498364843983857</v>
       </c>
       <c r="Y15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Y1</f>
-        <v>21.870972865231593</v>
+        <v>23.830247517741924</v>
       </c>
       <c r="Z15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Z1</f>
-        <v>20.440161556291208</v>
+        <v>22.271259362375627</v>
       </c>
       <c r="AA15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!AA1</f>
-        <v>19.1029547255058</v>
+        <v>20.814261086332362</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="B21" s="17">
         <f>SUM(B15:AA15) / SUM($B$15:$AA$18)</f>
-        <v>0.33580045315430895</v>
+        <v>0.35519748239815635</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
@@ -35368,7 +35368,7 @@
       </c>
       <c r="B22" s="17">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AA16) / SUM($B$15:$AA$18)</f>
-        <v>8.4966283341220597E-2</v>
+        <v>8.2484960536142585E-2</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="B23" s="17">
         <f t="shared" si="1"/>
-        <v>0.15980657867149367</v>
+        <v>0.15513964853796511</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
@@ -35386,7 +35386,7 @@
       </c>
       <c r="B24" s="17">
         <f t="shared" si="1"/>
-        <v>0.41942668483297668</v>
+        <v>0.40717790852773578</v>
       </c>
     </row>
   </sheetData>
@@ -35554,11 +35554,11 @@
       </c>
       <c r="E3" s="13">
         <f>'CO2 Corrected Production Cost'!B12</f>
-        <v>6.7150916431847465</v>
+        <v>6.9368857811157802</v>
       </c>
       <c r="F3" s="13">
         <f>'WACC Corrected Production Cost'!B12</f>
-        <v>6.6639403176472207</v>
+        <v>6.8857344555782563</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>148</v>
@@ -35576,11 +35576,11 @@
       </c>
       <c r="L3" s="13">
         <f>'CO2 Corrected Production Cost'!B23</f>
-        <v>11.137187787043441</v>
+        <v>11.688504644186299</v>
       </c>
       <c r="M3" s="13">
         <f>'WACC Corrected Production Cost'!B23</f>
-        <v>11.044653572742755</v>
+        <v>11.595970429885609</v>
       </c>
       <c r="O3" s="12" t="s">
         <v>148</v>
@@ -35598,11 +35598,11 @@
       </c>
       <c r="S3" s="13">
         <f>'CO2 Corrected Production Cost'!B34</f>
-        <v>10.94782044184528</v>
+        <v>11.349822316845287</v>
       </c>
       <c r="T3" s="13">
         <f>'WACC Corrected Production Cost'!B34</f>
-        <v>10.875476122878714</v>
+        <v>11.277477997878714</v>
       </c>
       <c r="V3" s="12" t="s">
         <v>148</v>
@@ -35620,11 +35620,11 @@
       </c>
       <c r="Z3" s="13">
         <f>'CO2 Corrected Production Cost'!B45</f>
-        <v>6.4276734480865887</v>
+        <v>6.7073269263474566</v>
       </c>
       <c r="AA3" s="13">
         <f>'WACC Corrected Production Cost'!B45</f>
-        <v>6.3797361158508838</v>
+        <v>6.6593895941117545</v>
       </c>
       <c r="AC3" s="12" t="s">
         <v>148</v>
@@ -35642,11 +35642,11 @@
       </c>
       <c r="AG3" s="13">
         <f>'CO2 Corrected Production Cost'!B56</f>
-        <v>6.7866690318389846</v>
+        <v>7.0704350612507527</v>
       </c>
       <c r="AH3" s="13">
         <f>'WACC Corrected Production Cost'!B56</f>
-        <v>6.7321119668055553</v>
+        <v>7.015877996217319</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
@@ -35666,11 +35666,11 @@
       </c>
       <c r="E4" s="16">
         <f>E3*Inputs!$C$6</f>
-        <v>6.0435824788662718</v>
+        <v>6.2431972030042022</v>
       </c>
       <c r="F4" s="16">
         <f>F3*Inputs!$C$6</f>
-        <v>5.9975462858824988</v>
+        <v>6.1971610100204311</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>148</v>
@@ -35688,11 +35688,11 @@
       </c>
       <c r="L4" s="16">
         <f>L3*Inputs!$C$6</f>
-        <v>10.023469008339097</v>
+        <v>10.51965417976767</v>
       </c>
       <c r="M4" s="16">
         <f>M3*Inputs!$C$6</f>
-        <v>9.9401882154684795</v>
+        <v>10.436373386897049</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>148</v>
@@ -35710,11 +35710,11 @@
       </c>
       <c r="S4" s="16">
         <f>S3*Inputs!$C$6</f>
-        <v>9.8530383976607521</v>
+        <v>10.214840085160759</v>
       </c>
       <c r="T4" s="16">
         <f>T3*Inputs!$C$6</f>
-        <v>9.7879285105908433</v>
+        <v>10.149730198090843</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>148</v>
@@ -35732,11 +35732,11 @@
       </c>
       <c r="Z4" s="16">
         <f>Z3*Inputs!$C$6</f>
-        <v>5.7849061032779296</v>
+        <v>6.0365942337127114</v>
       </c>
       <c r="AA4" s="16">
         <f>AA3*Inputs!$C$6</f>
-        <v>5.7417625042657958</v>
+        <v>5.9934506347005794</v>
       </c>
       <c r="AC4" s="12" t="s">
         <v>148</v>
@@ -35754,11 +35754,11 @@
       </c>
       <c r="AG4" s="16">
         <f>AG3*Inputs!$C$6</f>
-        <v>6.1080021286550865</v>
+        <v>6.3633915551256779</v>
       </c>
       <c r="AH4" s="16">
         <f>AH3*Inputs!$C$6</f>
-        <v>6.0589007701249997</v>
+        <v>6.3142901965955875</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
@@ -36338,11 +36338,11 @@
       </c>
       <c r="E10" s="13">
         <f>(E4-E5) / E9 * 10^6</f>
-        <v>1704.1396910378407</v>
+        <v>1769.0135393448031</v>
       </c>
       <c r="F10" s="13">
         <f>(F4-F5) / F9 * 10^6</f>
-        <v>1689.1781444226938</v>
+        <v>1754.0519927296568</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>156</v>
@@ -36360,11 +36360,11 @@
       </c>
       <c r="L10" s="13">
         <f>(L4-L5) / L9 * 10^6</f>
-        <v>2997.5841306050229</v>
+        <v>3158.8419821109023</v>
       </c>
       <c r="M10" s="13">
         <f>(M4-M5) / M9 * 10^6</f>
-        <v>2970.5182638614519</v>
+        <v>3131.7761153673296</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>156</v>
@@ -36382,11 +36382,11 @@
       </c>
       <c r="S10" s="13">
         <f>(S4-S5) / S9 * 10^6</f>
-        <v>2942.194982175421</v>
+        <v>3059.7788322317929</v>
       </c>
       <c r="T10" s="13">
         <f>(T4-T5) / T9 * 10^6</f>
-        <v>2921.0345745186287</v>
+        <v>3038.6184245749987</v>
       </c>
       <c r="V10" s="12" t="s">
         <v>156</v>
@@ -36404,11 +36404,11 @@
       </c>
       <c r="Z10" s="13">
         <f>(Z4-Z5) / Z9 * 10^6</f>
-        <v>1620.0710832586003</v>
+        <v>1701.868544167379</v>
       </c>
       <c r="AA10" s="13">
         <f>(AA4-AA5) / AA9 * 10^6</f>
-        <v>1606.0496161057283</v>
+        <v>1687.8470770145075</v>
       </c>
       <c r="AC10" s="12" t="s">
         <v>156</v>
@@ -36426,11 +36426,11 @@
       </c>
       <c r="AG10" s="13">
         <f>(AG4-AG5) / AG9 * 10^6</f>
-        <v>1725.0757748184114</v>
+        <v>1808.0761395640852</v>
       </c>
       <c r="AH10" s="13">
         <f>(AH4-AH5) / AH9 * 10^6</f>
-        <v>1709.1180637893112</v>
+        <v>1792.1184285349839</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
@@ -36584,11 +36584,11 @@
       </c>
       <c r="E14" s="13">
         <f>'CO2 Corrected Production Cost'!B68</f>
-        <v>1.7066963958622603</v>
+        <v>1.8138553613795019</v>
       </c>
       <c r="F14" s="13">
         <f>'WACC Corrected Production Cost'!B68</f>
-        <v>1.6874284786280427</v>
+        <v>1.7945874441452847</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>148</v>
@@ -36606,11 +36606,11 @@
       </c>
       <c r="L14" s="13">
         <f>'CO2 Corrected Production Cost'!B79</f>
-        <v>4.8864876915774014</v>
+        <v>5.1528542630059722</v>
       </c>
       <c r="M14" s="13">
         <f>'WACC Corrected Production Cost'!B79</f>
-        <v>4.8518810363076863</v>
+        <v>5.1182476077362598</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>148</v>
@@ -36628,11 +36628,11 @@
       </c>
       <c r="S14" s="13">
         <f>'CO2 Corrected Production Cost'!B90</f>
-        <v>3.388472518663046</v>
+        <v>3.5826981436630465</v>
       </c>
       <c r="T14" s="13">
         <f>'WACC Corrected Production Cost'!B90</f>
-        <v>3.3622434926102103</v>
+        <v>3.5564691176102081</v>
       </c>
       <c r="V14" s="12" t="s">
         <v>148</v>
@@ -36650,11 +36650,11 @@
       </c>
       <c r="Z14" s="13">
         <f>'CO2 Corrected Production Cost'!B101</f>
-        <v>1.5599599502503307</v>
+        <v>1.6950734285111995</v>
       </c>
       <c r="AA14" s="13">
         <f>'WACC Corrected Production Cost'!B101</f>
-        <v>1.5407264658637589</v>
+        <v>1.6758399441246277</v>
       </c>
       <c r="AC14" s="12" t="s">
         <v>148</v>
@@ -36672,11 +36672,11 @@
       </c>
       <c r="AG14" s="13">
         <f>'CO2 Corrected Production Cost'!B112</f>
-        <v>1.8533575305308503</v>
+        <v>1.9904579717073221</v>
       </c>
       <c r="AH14" s="13">
         <f>'WACC Corrected Production Cost'!B112</f>
-        <v>1.8333806384317852</v>
+        <v>1.9704810796082559</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
@@ -36696,11 +36696,11 @@
       </c>
       <c r="E15" s="16">
         <f>E14*Inputs!$C$6</f>
-        <v>1.5360267562760344</v>
+        <v>1.6324698252415517</v>
       </c>
       <c r="F15" s="16">
         <f>F14*Inputs!$C$6</f>
-        <v>1.5186856307652385</v>
+        <v>1.6151286997307563</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>148</v>
@@ -36718,11 +36718,11 @@
       </c>
       <c r="L15" s="16">
         <f>L14*Inputs!$C$6</f>
-        <v>4.3978389224196617</v>
+        <v>4.6375688367053751</v>
       </c>
       <c r="M15" s="16">
         <f>M14*Inputs!$C$6</f>
-        <v>4.3666929326769175</v>
+        <v>4.6064228469626336</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>148</v>
@@ -36740,11 +36740,11 @@
       </c>
       <c r="S15" s="16">
         <f>S14*Inputs!$C$6</f>
-        <v>3.0496252667967414</v>
+        <v>3.2244283292967419</v>
       </c>
       <c r="T15" s="16">
         <f>T14*Inputs!$C$6</f>
-        <v>3.0260191433491892</v>
+        <v>3.2008222058491875</v>
       </c>
       <c r="V15" s="12" t="s">
         <v>148</v>
@@ -36762,11 +36762,11 @@
       </c>
       <c r="Z15" s="16">
         <f>Z14*Inputs!$C$6</f>
-        <v>1.4039639552252976</v>
+        <v>1.5255660856600795</v>
       </c>
       <c r="AA15" s="16">
         <f>AA14*Inputs!$C$6</f>
-        <v>1.3866538192773832</v>
+        <v>1.508255949712165</v>
       </c>
       <c r="AC15" s="12" t="s">
         <v>148</v>
@@ -36784,11 +36784,11 @@
       </c>
       <c r="AG15" s="16">
         <f>AG14*Inputs!$C$6</f>
-        <v>1.6680217774777653</v>
+        <v>1.7914121745365899</v>
       </c>
       <c r="AH15" s="16">
         <f>AH14*Inputs!$C$6</f>
-        <v>1.6500425745886067</v>
+        <v>1.7734329716474304</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
@@ -36800,19 +36800,19 @@
       </c>
       <c r="C16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="F16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>150</v>
@@ -36822,19 +36822,19 @@
       </c>
       <c r="J16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="M16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>150</v>
@@ -36844,19 +36844,19 @@
       </c>
       <c r="Q16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="R16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="S16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="T16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="V16" s="12" t="s">
         <v>150</v>
@@ -36866,19 +36866,19 @@
       </c>
       <c r="X16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="Y16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" s="12" t="s">
         <v>150</v>
@@ -36896,11 +36896,11 @@
       </c>
       <c r="AG16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" s="16">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
@@ -37360,19 +37360,19 @@
       </c>
       <c r="C21" s="13">
         <f>(C15-C16) / C20 * 10^6</f>
-        <v>336.62719611942896</v>
+        <v>44.131420928405902</v>
       </c>
       <c r="D21" s="13">
         <f>(D15-D16) / D20 * 10^6</f>
-        <v>-57.729872895144979</v>
+        <v>-350.22564808616795</v>
       </c>
       <c r="E21" s="13">
         <f>(E15-E16) / E20 * 10^6</f>
-        <v>239.20524070921428</v>
+        <v>-21.946989794175089</v>
       </c>
       <c r="F21" s="13">
         <f>(F15-F16) / F20 * 10^6</f>
-        <v>233.56945632147534</v>
+        <v>-27.582774181913884</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>156</v>
@@ -37382,19 +37382,19 @@
       </c>
       <c r="J21" s="13">
         <f>(J15-J16) / J20 * 10^6</f>
-        <v>1100.8391122119124</v>
+        <v>808.34333702088918</v>
       </c>
       <c r="K21" s="13">
         <f>(K15-K16) / K20 * 10^6</f>
-        <v>422.57914612233822</v>
+        <v>130.08337093131516</v>
       </c>
       <c r="L21" s="13">
         <f>(L15-L16) / L20 * 10^6</f>
-        <v>1169.2807606950823</v>
+        <v>954.69608229903395</v>
       </c>
       <c r="M21" s="13">
         <f>(M15-M16) / M20 * 10^6</f>
-        <v>1159.1584602351984</v>
+        <v>944.5737818391508</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>156</v>
@@ -37404,19 +37404,19 @@
       </c>
       <c r="Q21" s="13">
         <f>(Q15-Q16) / Q20 * 10^6</f>
-        <v>953.2316124214982</v>
+        <v>660.73583723047523</v>
       </c>
       <c r="R21" s="13">
         <f>(R15-R16) / R20 * 10^6</f>
-        <v>187.39075334003499</v>
+        <v>-105.10502185098805</v>
       </c>
       <c r="S21" s="13">
         <f>(S15-S16) / S20 * 10^6</f>
-        <v>731.11765144558319</v>
+        <v>495.43205100089642</v>
       </c>
       <c r="T21" s="13">
         <f>(T15-T16) / T20 * 10^6</f>
-        <v>723.44577213775369</v>
+        <v>487.7601716930659</v>
       </c>
       <c r="V21" s="12" t="s">
         <v>156</v>
@@ -37426,19 +37426,19 @@
       </c>
       <c r="X21" s="13">
         <f>(X15-X16) / X20 * 10^6</f>
-        <v>175.01350105543972</v>
+        <v>-117.48227413558332</v>
       </c>
       <c r="Y21" s="13">
         <f>(Y15-Y16) / Y20 * 10^6</f>
-        <v>-191.61607410716172</v>
+        <v>-484.11184929818478</v>
       </c>
       <c r="Z21" s="13">
         <f>(Z15-Z16) / Z20 * 10^6</f>
-        <v>196.28545030117752</v>
+        <v>-56.690203327177294</v>
       </c>
       <c r="AA21" s="13">
         <f>(AA15-AA16) / AA20 * 10^6</f>
-        <v>190.65973737590284</v>
+        <v>-62.315916252451991</v>
       </c>
       <c r="AC21" s="12" t="s">
         <v>156</v>
@@ -37456,25 +37456,25 @@
       </c>
       <c r="AG21" s="13">
         <f>(AG15-AG16) / AG20 * 10^6</f>
-        <v>282.10300298449852</v>
+        <v>29.708527614418848</v>
       </c>
       <c r="AH21" s="13">
         <f>(AH15-AH16) / AH20 * 10^6</f>
-        <v>276.25984644407509</v>
+        <v>23.865371073995103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="O12:T12"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="V12:AA12"/>
     <mergeCell ref="H12:M12"/>
     <mergeCell ref="AC12:AH12"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Marchese_2021_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Marchese_2021_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{8C94FA30-1442-A847-B461-8BCABFE5E32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32AFFADF-2F08-4B85-9DC4-EA34F3A8C042}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -829,7 +829,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1177,13 +1177,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,12 +1197,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1237,12 +1237,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -1272,12 +1272,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1358,12 +1358,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -1378,12 +1378,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1413,12 +1413,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1448,12 +1448,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1483,12 +1483,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -1518,12 +1518,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C33" s="4">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1561,17 +1561,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -1619,12 +1619,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1661,12 +1661,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1924,12 +1924,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>65</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -2059,12 +2059,12 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2112,14 +2112,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T44"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="30.625" customWidth="1"/>
+    <col min="1" max="1" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="20">
         <v>2021</v>
       </c>
@@ -2143,7 +2143,7 @@
       <c r="S1" s="19"/>
       <c r="T1" s="19"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>76</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>89</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>90</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>94</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>95</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="S14" s="19"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>83</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>100</v>
       </c>
@@ -2890,12 +2890,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>102</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>103</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>108</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
         <v>109</v>
       </c>
@@ -3101,7 +3101,7 @@
       <c r="S31" s="19"/>
       <c r="T31" s="19"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>112</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>113</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="20" t="s">
         <v>114</v>
       </c>
@@ -3308,7 +3308,7 @@
       <c r="S38" s="19"/>
       <c r="T38" s="19"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>117</v>
       </c>
@@ -3492,29 +3492,29 @@
       </c>
       <c r="M42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>112.968</v>
+        <v>107.352</v>
       </c>
       <c r="N42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>112.968</v>
+        <v>107.352</v>
       </c>
       <c r="O42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>112.968</v>
+        <v>107.352</v>
       </c>
       <c r="P42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>112.968</v>
+        <v>107.352</v>
       </c>
       <c r="Q42" s="8">
         <f>('Study Parameters'!$C$19*Inputs!$C$33) / 10^6</f>
-        <v>112.968</v>
+        <v>107.352</v>
       </c>
       <c r="R42" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>118</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="L44" t="s">
         <v>118</v>
       </c>
@@ -3616,18 +3616,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA167"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="11">
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3710,12 +3710,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>494420000</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>56800000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>437620000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>71760516.434274063</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>8.6989531048119826</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -4384,12 +4384,12 @@
         <v>6.9852593431640226</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>1996440000</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>56800000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>1939640000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>318060344.81188095</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>30.279700231248764</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>127</v>
       </c>
@@ -5058,12 +5058,12 @@
         <v>24.314599285692758</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>120</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>354300000</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>149899999.99999997</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>204400000.00000003</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>33517319.956047758</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>12.186988838103453</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -5732,12 +5732,12 @@
         <v>9.7861520369970734</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>1393570000</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>149899999.99999997</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>1243670000</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>203935838.11026374</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>49.303774552389157</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -6406,12 +6406,12 @@
         <v>39.590930965568496</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>397799999.99999994</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>316799999.99999994</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>123</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>51948566.350665003</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>124</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>11.973997446077165</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -7080,12 +7080,12 @@
         <v>9.6151199491999648</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>120</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>1604800000</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>122</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>1523800000</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>249871292.31421509</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>125</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>126</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>43.406289112743835</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>127</v>
       </c>
@@ -7754,12 +7754,12 @@
         <v>34.855250157533298</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>120</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>358100000</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>121</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>122</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>254900000</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>123</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>41798262.508789495</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>124</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>125</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>126</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>6.9579019985773076</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>127</v>
       </c>
@@ -8428,12 +8428,12 @@
         <v>5.5871953048575786</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>120</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>1465600000</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>121</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>122</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>1362400000</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>123</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>223405071.9575316</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>124</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>125</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>126</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>27.021307795678752</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>127</v>
       </c>
@@ -9102,12 +9102,12 @@
         <v>21.698110159930039</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>440100000</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>304900000</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>49997215.531306066</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>8.0498239784515508</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -9776,12 +9776,12 @@
         <v>6.4640086546965954</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>120</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>1839900000</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>121</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>1704700000</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>123</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>279535104.34968007</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>124</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>125</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>126</v>
       </c>
@@ -10441,7 +10441,7 @@
         <v>33.781441625510375</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>127</v>
       </c>
@@ -10450,17 +10450,17 @@
         <v>27.126497625284834</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="11">
         <v>2050</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>275113167.50580031</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>121</v>
       </c>
@@ -10677,7 +10677,7 @@
         <v>149900000</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>122</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>125213167.50580031</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>123</v>
       </c>
@@ -10895,7 +10895,7 @@
         <v>20532337.563611109</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>2.5401839612676809</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -11130,12 +11130,12 @@
         <v>2.0397677208979479</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>120</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>202948901.6556448</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>121</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>122</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>121948901.6556448</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>19997066.316442508</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>124</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>125</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>126</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>5.7938926152230383</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>127</v>
       </c>
@@ -11805,12 +11805,12 @@
         <v>4.6524957700240996</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>120</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>260016813.71233764</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>121</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>122</v>
       </c>
@@ -12136,7 +12136,7 @@
         <v>156816813.71233764</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>123</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>25714673.775363784</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>124</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>125</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>126</v>
       </c>
@@ -12471,7 +12471,7 @@
         <v>5.1654389241153709</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>127</v>
       </c>
@@ -12480,12 +12480,12 @@
         <v>4.1478474560646434</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>120</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>196348294.00716552</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>121</v>
       </c>
@@ -12702,7 +12702,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>122</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>61148294.007165521</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>123</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>10027039.799435636</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>124</v>
       </c>
@@ -13028,7 +13028,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>125</v>
       </c>
@@ -13137,7 +13137,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>126</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>1.8520974931632403</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>127</v>
       </c>
@@ -13155,12 +13155,12 @@
         <v>1.4872342870100821</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>120</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>235192009.97490495</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>121</v>
       </c>
@@ -13377,7 +13377,7 @@
         <v>133699999.99999999</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>122</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>101492009.97490497</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>123</v>
       </c>
@@ -13595,7 +13595,7 @@
         <v>16642564.438900586</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>124</v>
       </c>
@@ -13703,7 +13703,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>125</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>126</v>
       </c>
@@ -13821,7 +13821,7 @@
         <v>2.6143502739660383</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>127</v>
       </c>
@@ -13838,18 +13838,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AA112"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13932,12 +13932,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>272538856.00618696</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>56800000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>215738856.00618696</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>35376654.910523891</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -14588,7 +14588,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>5.5110056336365068</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -14606,12 +14606,12 @@
         <v>4.4253375238101151</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -14720,7 +14720,7 @@
         <v>197815639.09935448</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -14828,7 +14828,7 @@
         <v>149899999.99999997</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>47915639.099354506</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -15046,7 +15046,7 @@
         <v>7857161.4803893184</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>6.5982616630804083</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>127</v>
       </c>
@@ -15280,12 +15280,12 @@
         <v>5.2984041154535682</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>120</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>258544078.62649351</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -15611,7 +15611,7 @@
         <v>177544078.62649351</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>29113511.201692183</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -15828,7 +15828,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -15936,7 +15936,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>8.3475411603087686</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -15954,12 +15954,12 @@
         <v>6.7030755517279417</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>201542180.27430987</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -16285,7 +16285,7 @@
         <v>98342180.274309874</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>16126058.324018454</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -16502,7 +16502,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -16619,7 +16619,7 @@
         <v>4.1217096122423422</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -16628,12 +16628,12 @@
         <v>3.309732818630601</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>242242143.97323194</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -16850,7 +16850,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -16959,7 +16959,7 @@
         <v>107042143.97323194</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>123</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>17552670.197319686</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>124</v>
       </c>
@@ -17176,7 +17176,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -17284,7 +17284,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>4.4127310367830228</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -17302,17 +17302,17 @@
         <v>3.5434230225367673</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>2050</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>158253747.37606341</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>149900000</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>8353747.3760634065</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -17747,7 +17747,7 @@
         <v>1369839.6459662993</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>126</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>0.86116930423123084</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>127</v>
       </c>
@@ -17982,12 +17982,12 @@
         <v>0.69151895129767837</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>120</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>122091631.97020155</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>121</v>
       </c>
@@ -18204,7 +18204,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>122</v>
       </c>
@@ -18313,7 +18313,7 @@
         <v>41091631.970201552</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>123</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>6738167.202844454</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>124</v>
       </c>
@@ -18530,7 +18530,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>125</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>126</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>2.9061329836000671</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>127</v>
       </c>
@@ -18657,12 +18657,12 @@
         <v>2.3336247858308541</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>120</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>134808082.51392856</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>121</v>
       </c>
@@ -18879,7 +18879,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>122</v>
       </c>
@@ -18988,7 +18988,7 @@
         <v>31608082.513928562</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>123</v>
       </c>
@@ -19097,7 +19097,7 @@
         <v>5183063.6732705571</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>124</v>
       </c>
@@ -19205,7 +19205,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>125</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>126</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>1.9047948824901333</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>127</v>
       </c>
@@ -19332,12 +19332,12 @@
         <v>1.529550290639577</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -19446,7 +19446,7 @@
         <v>110183187.23464699</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -19554,7 +19554,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -19663,7 +19663,7 @@
         <v>-25016812.765353009</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -19772,7 +19772,7 @@
         <v>-4102233.4527244451</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -19880,7 +19880,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -19989,7 +19989,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>0.29113541395094822</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>127</v>
       </c>
@@ -20007,12 +20007,12 @@
         <v>0.23378173740261143</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>120</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>126287868.49539924</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>121</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>133699999.99999999</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>122</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>-7412131.5046007484</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>123</v>
       </c>
@@ -20447,7 +20447,7 @@
         <v>-1215434.3600587326</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>124</v>
       </c>
@@ -20555,7 +20555,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>125</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>126</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>0.61243590853394891</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>127</v>
       </c>
@@ -20690,19 +20690,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AA112"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -20785,12 +20785,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -20899,7 +20899,7 @@
         <v>556074856.00618696</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -21007,7 +21007,7 @@
         <v>56800000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -21116,7 +21116,7 @@
         <v>499274856.00618696</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -21225,7 +21225,7 @@
         <v>81870621.794369072</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -21333,7 +21333,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -21441,7 +21441,7 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>8.6387120561840351</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -21459,12 +21459,12 @@
         <v>6.9368857811157802</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -21573,7 +21573,7 @@
         <v>483251639.09935451</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -21681,7 +21681,7 @@
         <v>149899999.99999997</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -21790,7 +21790,7 @@
         <v>333351639.09935451</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -21899,7 +21899,7 @@
         <v>54662688.579090133</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -22007,7 +22007,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -22115,7 +22115,7 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -22124,7 +22124,7 @@
         <v>14.556045634104979</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>127</v>
       </c>
@@ -22133,12 +22133,12 @@
         <v>11.688504644186299</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>120</v>
       </c>
@@ -22247,7 +22247,7 @@
         <v>544180078.62649345</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -22355,7 +22355,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -22464,7 +22464,7 @@
         <v>463180078.62649345</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -22573,7 +22573,7 @@
         <v>75951834.112483054</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -22681,7 +22681,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -22789,7 +22789,7 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>14.134274367179685</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -22807,12 +22807,12 @@
         <v>11.349822316845287</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>488478180.27430993</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>385278180.27430993</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>63177554.013394773</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -23355,7 +23355,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -23463,7 +23463,7 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -23472,7 +23472,7 @@
         <v>8.3528355247166335</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -23481,12 +23481,12 @@
         <v>6.7073269263474566</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -23595,7 +23595,7 @@
         <v>529178143.97323197</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -23703,7 +23703,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -23812,7 +23812,7 @@
         <v>393978143.97323197</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>123</v>
       </c>
@@ -23921,7 +23921,7 @@
         <v>64604165.886696003</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>124</v>
       </c>
@@ -24029,7 +24029,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -24137,7 +24137,7 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -24146,7 +24146,7 @@
         <v>8.805024982877649</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -24155,17 +24155,17 @@
         <v>7.0704350612507527</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>2050</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -24175,106 +24175,106 @@
       </c>
       <c r="C60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="D60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="E60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="F60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="G60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="H60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="I60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="J60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="K60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="L60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="M60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="N60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="O60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="P60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Q60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="R60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="S60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="T60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="U60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="V60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="W60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="X60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Y60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Z60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="AA60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+        <v>263085747.37606341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -24382,7 +24382,7 @@
         <v>149900000</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -24392,106 +24392,106 @@
       </c>
       <c r="C62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="D62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="E62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="F62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="G62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="H62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="I62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="J62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="K62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="L62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="M62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="N62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="O62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="P62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Q62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="R62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="S62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="T62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="U62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="V62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="W62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="X62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Y62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Z62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="AA62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+        <v>113185747.37606341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -24501,106 +24501,106 @@
       </c>
       <c r="C63">
         <f>C62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>110513253.37308225</v>
+        <v>105289067.32657062</v>
       </c>
       <c r="D63">
         <f>D62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>102803026.39356488</v>
+        <v>97943318.443321511</v>
       </c>
       <c r="E63">
         <f>E62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>95630722.226571992</v>
+        <v>91110063.668206051</v>
       </c>
       <c r="F63">
         <f>F62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>88958811.373555332</v>
+        <v>84753547.598331213</v>
       </c>
       <c r="G63">
         <f>G62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>82752382.673074722</v>
+        <v>78840509.393796474</v>
       </c>
       <c r="H63">
         <f>H62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>76978960.626116037</v>
+        <v>73340008.738415331</v>
       </c>
       <c r="I63">
         <f>I62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>71608335.466154441</v>
+        <v>68223263.942711934</v>
       </c>
       <c r="J63">
         <f>J62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>66612405.084794842</v>
+        <v>63463501.342057616</v>
       </c>
       <c r="K63">
         <f>K62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>61965027.985855661</v>
+        <v>59035815.201914065</v>
       </c>
       <c r="L63">
         <f>L62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>57641886.498470396</v>
+        <v>54917037.397129372</v>
       </c>
       <c r="M63">
         <f>M62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>53620359.533460826</v>
+        <v>51085616.183376156</v>
       </c>
       <c r="N63">
         <f>N62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>49879404.217172861</v>
+        <v>47521503.426396422</v>
       </c>
       <c r="O63">
         <f>O62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>46399445.783416614</v>
+        <v>44206049.698973417</v>
       </c>
       <c r="P63">
         <f>P62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>43162275.147364296</v>
+        <v>41121906.69671946</v>
       </c>
       <c r="Q63">
         <f>Q62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>40150953.625455163</v>
+        <v>38252936.462064616</v>
       </c>
       <c r="R63">
         <f>R62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>37349724.302748986</v>
+        <v>35584126.941455454</v>
       </c>
       <c r="S63">
         <f>S62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>34743929.583952554</v>
+        <v>33101513.433912054</v>
       </c>
       <c r="T63">
         <f>T62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>32319934.496700048</v>
+        <v>30792105.519918192</v>
       </c>
       <c r="U63">
         <f>U62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>30065055.345767487</v>
+        <v>28643819.088295992</v>
       </c>
       <c r="V63">
         <f>V62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>27967493.34489999</v>
+        <v>26645413.105391622</v>
       </c>
       <c r="W63">
         <f>W62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>26016272.878976729</v>
+        <v>24786430.795713134</v>
       </c>
       <c r="X63">
         <f>X62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>24201184.073466729</v>
+        <v>23057144.926244777</v>
       </c>
       <c r="Y63">
         <f>Y62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>22512729.370666724</v>
+        <v>21448506.908134677</v>
       </c>
       <c r="Z63">
         <f>Z62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>20942073.833178349</v>
+        <v>19952099.449427608</v>
       </c>
       <c r="AA63">
         <f>AA62/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>19480998.91458451</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+        <v>18560092.511095449</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -24708,7 +24708,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -24817,30 +24817,30 @@
         <v>11412942.60734307</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>126</v>
       </c>
       <c r="B67">
         <f>SUM(B63:AA63) / SUM(C65:AA65)</f>
-        <v>2.2588485197752202</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+        <v>2.1781588646028065</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>127</v>
       </c>
       <c r="B68">
         <f>B67 * Inputs!$C$15</f>
-        <v>1.8138553613795019</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+        <v>1.7490615682760537</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>120</v>
       </c>
@@ -24850,106 +24850,106 @@
       </c>
       <c r="C71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="D71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="E71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="F71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="G71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="H71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="I71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="J71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="K71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="L71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="M71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="N71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="O71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="P71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Q71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="R71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="S71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="T71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="U71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="V71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="W71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="X71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Y71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Z71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="AA71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+        <v>227303631.97020152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>121</v>
       </c>
@@ -25057,7 +25057,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>122</v>
       </c>
@@ -25067,106 +25067,106 @@
       </c>
       <c r="C73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="D73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="G73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="H73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="I73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="J73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="K73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="L73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="M73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="N73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="O73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="P73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Q73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="R73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="S73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="T73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="U73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="V73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="W73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="X73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Y73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Z73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="AA73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+        <v>146303631.97020152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>123</v>
       </c>
@@ -25176,106 +25176,106 @@
       </c>
       <c r="C74">
         <f>C73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>141320587.87925726</v>
+        <v>136096401.83274561</v>
       </c>
       <c r="D74">
         <f>D73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>131461011.98070444</v>
+        <v>126601304.03046104</v>
       </c>
       <c r="E74">
         <f>E73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>122289313.47042273</v>
+        <v>117768654.91205677</v>
       </c>
       <c r="F74">
         <f>F73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>113757500.90271883</v>
+        <v>109552237.12749468</v>
       </c>
       <c r="G74">
         <f>G73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>105820931.07229657</v>
+        <v>101909057.7930183</v>
       </c>
       <c r="H74">
         <f>H73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>98438075.416089848</v>
+        <v>94799123.528389126</v>
       </c>
       <c r="I74">
         <f>I73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>91570302.712641716</v>
+        <v>88185231.189199179</v>
       </c>
       <c r="J74">
         <f>J73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>85181676.941992298</v>
+        <v>82032773.199255064</v>
       </c>
       <c r="K74">
         <f>K73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>79238769.248364925</v>
+        <v>76309556.464423314</v>
       </c>
       <c r="L74">
         <f>L73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>73710483.021734834</v>
+        <v>70985633.920393795</v>
       </c>
       <c r="M74">
         <f>M73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>68567891.183009133</v>
+        <v>66033147.832924448</v>
       </c>
       <c r="N74">
         <f>N73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>63784084.821403854</v>
+        <v>61426184.0306274</v>
       </c>
       <c r="O74">
         <f>O73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>59334032.392003581</v>
+        <v>57140636.307560369</v>
       </c>
       <c r="P74">
         <f>P73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>55194448.736747518</v>
+        <v>53154080.286102675</v>
       </c>
       <c r="Q74">
         <f>Q73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>51343673.243486069</v>
+        <v>49445656.080095507</v>
       </c>
       <c r="R74">
         <f>R73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>47761556.505568437</v>
+        <v>45995959.144274898</v>
       </c>
       <c r="S74">
         <f>S73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>44429354.888900876</v>
+        <v>42786938.738860369</v>
       </c>
       <c r="T74">
         <f>T73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>41329632.454791516</v>
+        <v>39801803.478009649</v>
       </c>
       <c r="U74">
         <f>U73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>38446169.725387454</v>
+        <v>37024933.467915952</v>
       </c>
       <c r="V74">
         <f>V73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>35763878.814313911</v>
+        <v>34441798.574805535</v>
       </c>
       <c r="W74">
         <f>W73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>33268724.478431541</v>
+        <v>32038882.395167939</v>
       </c>
       <c r="X74">
         <f>X73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>30947650.67761074</v>
+        <v>29803611.530388784</v>
       </c>
       <c r="Y74">
         <f>Y73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>28788512.258242548</v>
+        <v>27724289.795710497</v>
       </c>
       <c r="Z74">
         <f>Z73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>26780011.403016325</v>
+        <v>25790037.019265581</v>
       </c>
       <c r="AA74">
         <f>AA73/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>24911638.51443379</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+        <v>23990732.110944726</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>124</v>
       </c>
@@ -25383,7 +25383,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>125</v>
       </c>
@@ -25492,30 +25492,30 @@
         <v>4591413.6926092813</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>126</v>
       </c>
       <c r="B78">
         <f>SUM(B74:AA74) / SUM(C76:AA76)</f>
-        <v>6.4170040635192676</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+        <v>6.2164326349478385</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>127</v>
       </c>
       <c r="B79">
         <f>B78 * Inputs!$C$15</f>
-        <v>5.1528542630059722</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+        <v>4.9917954058631144</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>120</v>
       </c>
@@ -25525,106 +25525,106 @@
       </c>
       <c r="C82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="D82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="E82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="F82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="G82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="H82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="I82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="J82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="K82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="L82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="M82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="N82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="O82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="P82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Q82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="R82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="S82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="T82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="U82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="V82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="W82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="X82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Y82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Z82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="AA82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+        <v>240060082.51392856</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>121</v>
       </c>
@@ -25732,7 +25732,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>122</v>
       </c>
@@ -25742,106 +25742,106 @@
       </c>
       <c r="C84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="D84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="E84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="F84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="G84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="H84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="I84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="J84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="K84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="L84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="M84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="N84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="O84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="P84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Q84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="R84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="S84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="T84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="U84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="V84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="W84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="X84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Y84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Z84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="AA84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+        <v>136860082.51392856</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>123</v>
       </c>
@@ -25851,106 +25851,106 @@
       </c>
       <c r="C85">
         <f>C84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>132535890.71063122</v>
+        <v>127311704.6641196</v>
       </c>
       <c r="D85">
         <f>D84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>123289200.6610523</v>
+        <v>118429492.71080893</v>
       </c>
       <c r="E85">
         <f>E84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>114687628.52190913</v>
+        <v>110166969.96354319</v>
       </c>
       <c r="F85">
         <f>F84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>106686166.06689221</v>
+        <v>102480902.29166809</v>
       </c>
       <c r="G85">
         <f>G84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>99242945.178504378</v>
+        <v>95331071.899226129</v>
       </c>
       <c r="H85">
         <f>H84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>92319018.770701766</v>
+        <v>88680066.883001059</v>
       </c>
       <c r="I85">
         <f>I84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>85878156.996001631</v>
+        <v>82493085.472559124</v>
       </c>
       <c r="J85">
         <f>J84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>79886657.670699194</v>
+        <v>76737753.927961975</v>
       </c>
       <c r="K85">
         <f>K84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>74313169.926231816</v>
+        <v>71383957.142290205</v>
       </c>
       <c r="L85">
         <f>L84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>69128530.163936585</v>
+        <v>66403681.062595561</v>
       </c>
       <c r="M85">
         <f>M84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>64305609.454824716</v>
+        <v>61770866.104740046</v>
       </c>
       <c r="N85">
         <f>N84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>59819171.585883461</v>
+        <v>57461270.795107022</v>
       </c>
       <c r="O85">
         <f>O84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>55645741.010124147</v>
+        <v>53452344.92568095</v>
       </c>
       <c r="P85">
         <f>P84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>51763480.009417817</v>
+        <v>49723111.558772981</v>
       </c>
       <c r="Q85">
         <f>Q84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>48152074.427365415</v>
+        <v>46254057.263974868</v>
       </c>
       <c r="R85">
         <f>R84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>44792627.374293409</v>
+        <v>43027030.012999877</v>
       </c>
       <c r="S85">
         <f>S84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>41667560.348179922</v>
+        <v>40025144.198139422</v>
       </c>
       <c r="T85">
         <f>T84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>38760521.254120857</v>
+        <v>37232692.277339004</v>
       </c>
       <c r="U85">
         <f>U84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>36056298.841042653</v>
+        <v>34635062.583571158</v>
       </c>
       <c r="V85">
         <f>V84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>33540743.107946657</v>
+        <v>32218662.868438292</v>
       </c>
       <c r="W85">
         <f>W84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>31200691.263206191</v>
+        <v>29970849.179942593</v>
       </c>
       <c r="X85">
         <f>X84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>29023898.849494133</v>
+        <v>27879859.702272184</v>
       </c>
       <c r="Y85">
         <f>Y84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>26998975.673948031</v>
+        <v>25934753.211415984</v>
       </c>
       <c r="Z85">
         <f>Z84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>25115326.208323751</v>
+        <v>24125351.82457301</v>
       </c>
       <c r="AA85">
         <f>AA84/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>23363094.147277907</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+        <v>22442187.743788846</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>124</v>
       </c>
@@ -26058,7 +26058,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>125</v>
       </c>
@@ -26167,30 +26167,30 @@
         <v>6296795.9212927287</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>126</v>
       </c>
       <c r="B89">
         <f>SUM(B85:AA85) / SUM(C87:AA87)</f>
-        <v>4.4616415238643166</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+        <v>4.3153915238643163</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>127</v>
       </c>
       <c r="B90">
         <f>B89 * Inputs!$C$15</f>
-        <v>3.5826981436630465</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+        <v>3.4652593936630463</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -26200,106 +26200,106 @@
       </c>
       <c r="C93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="D93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="E93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="F93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="G93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="H93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="I93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="J93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="K93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="L93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="M93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="N93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="O93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="P93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Q93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="R93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="S93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="T93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="U93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="V93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="W93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="X93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Y93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Z93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="AA93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+        <v>215695187.23464701</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -26407,7 +26407,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -26417,106 +26417,106 @@
       </c>
       <c r="C95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="D95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="E95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="F95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="G95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="H95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="I95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="J95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="K95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="L95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="M95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="N95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="O95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="P95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Q95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="R95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="S95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="T95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="U95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="V95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="W95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="X95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Y95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Z95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="AA95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+        <v>80495187.234647006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -26526,106 +26526,106 @@
       </c>
       <c r="C96">
         <f>C95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>80103429.985718116</v>
+        <v>74879243.939206526</v>
       </c>
       <c r="D96">
         <f>D95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>74514818.591365695</v>
+        <v>69655110.641122341</v>
       </c>
       <c r="E96">
         <f>E95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>69316110.317549482</v>
+        <v>64795451.759183578</v>
       </c>
       <c r="F96">
         <f>F95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>64480102.620976269</v>
+        <v>60274838.845752165</v>
       </c>
       <c r="G96">
         <f>G95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>59981490.810210481</v>
+        <v>56069617.530932248</v>
       </c>
       <c r="H96">
         <f>H95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>55796735.637405105</v>
+        <v>52157783.749704421</v>
       </c>
       <c r="I96">
         <f>I95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>51903940.127818696</v>
+        <v>48518868.604376204</v>
       </c>
       <c r="J96">
         <f>J95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>48282735.002622046</v>
+        <v>45133831.259884842</v>
       </c>
       <c r="K96">
         <f>K95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>44914172.095462367</v>
+        <v>41984959.311520785</v>
       </c>
       <c r="L96">
         <f>L95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>41780625.205081284</v>
+        <v>39055776.103740275</v>
       </c>
       <c r="M96">
         <f>M95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>38865697.865191884</v>
+        <v>36330954.515107229</v>
       </c>
       <c r="N96">
         <f>N95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>36154137.549015708</v>
+        <v>33796236.758239284</v>
       </c>
       <c r="O96">
         <f>O95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>33631755.859549493</v>
+        <v>31438359.775106307</v>
       </c>
       <c r="P96">
         <f>P95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>31285354.287953019</v>
+        <v>29244985.837308194</v>
       </c>
       <c r="Q96">
         <f>Q95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>29102655.151584204</v>
+        <v>27204637.988193668</v>
       </c>
       <c r="R96">
         <f>R95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>27072237.350310892</v>
+        <v>25306639.989017367</v>
       </c>
       <c r="S96">
         <f>S95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>25183476.604940366</v>
+        <v>23541060.454899881</v>
       </c>
       <c r="T96">
         <f>T95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>23426489.865060806</v>
+        <v>21898660.888278957</v>
       </c>
       <c r="U96">
         <f>U95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>21792083.5954054</v>
+        <v>20370847.337933913</v>
       </c>
       <c r="V96">
         <f>V95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>20271705.670144558</v>
+        <v>18949625.430636201</v>
       </c>
       <c r="W96">
         <f>W95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>18857400.623390287</v>
+        <v>17627558.540126696</v>
       </c>
       <c r="X96">
         <f>X95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>17541768.021758407</v>
+        <v>16397728.874536462</v>
       </c>
       <c r="Y96">
         <f>Y95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>16317923.741170611</v>
+        <v>15253701.27863857</v>
       </c>
       <c r="Z96">
         <f>Z95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>15179463.945274988</v>
+        <v>14189489.561524253</v>
       </c>
       <c r="AA96">
         <f>AA95/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>14120431.576999988</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+        <v>13199525.173510931</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -26733,7 +26733,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -26842,30 +26842,30 @@
         <v>9051644.1368582975</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
       <c r="B100">
         <f>SUM(B96:AA96) / SUM(C98:AA98)</f>
-        <v>2.1109258138371101</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+        <v>2.0091866834023282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>127</v>
       </c>
       <c r="B101">
         <f>B100 * Inputs!$C$15</f>
-        <v>1.6950734285111995</v>
-      </c>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+        <v>1.6133769067720696</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>120</v>
       </c>
@@ -26875,106 +26875,106 @@
       </c>
       <c r="C104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="D104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="E104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="F104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="G104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="H104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="I104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="J104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="K104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="L104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="M104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="N104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="O104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="P104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Q104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="R104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="S104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="T104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="U104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="V104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="W104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="X104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Y104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Z104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="AA104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+        <v>231799868.49539924</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>121</v>
       </c>
@@ -27082,7 +27082,7 @@
         <v>133699999.99999999</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>122</v>
       </c>
@@ -27092,106 +27092,106 @@
       </c>
       <c r="C106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="D106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="E106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="F106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="G106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="H106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="I106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="J106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="K106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="L106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="M106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="N106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="O106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="P106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Q106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="R106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="S106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="T106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="U106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="V106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="W106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="X106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Y106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Z106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="AA106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+        <v>98099868.495399252</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>123</v>
       </c>
@@ -27201,106 +27201,106 @@
       </c>
       <c r="C107">
         <f>C106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!C$2</f>
-        <v>96479877.670138866</v>
+        <v>91255691.623627216</v>
       </c>
       <c r="D107">
         <f>D106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!D$2</f>
-        <v>89748723.414082676</v>
+        <v>84889015.463839278</v>
       </c>
       <c r="E107">
         <f>E106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!E$2</f>
-        <v>83487184.571239695</v>
+        <v>78966526.012873739</v>
       </c>
       <c r="F107">
         <f>F106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!F$2</f>
-        <v>77662497.275571808</v>
+        <v>73457233.500347674</v>
       </c>
       <c r="G107">
         <f>G106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!G$2</f>
-        <v>72244183.512159824</v>
+        <v>68332310.232881546</v>
       </c>
       <c r="H107">
         <f>H106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!H$2</f>
-        <v>67203891.63921845</v>
+        <v>63564939.751517728</v>
       </c>
       <c r="I107">
         <f>I106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!I$2</f>
-        <v>62515248.036482275</v>
+        <v>59130176.513039745</v>
       </c>
       <c r="J107">
         <f>J106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!J$2</f>
-        <v>58153719.103704445</v>
+        <v>55004815.360967204</v>
       </c>
       <c r="K107">
         <f>K106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!K$2</f>
-        <v>54096482.887166925</v>
+        <v>51167270.103225306</v>
       </c>
       <c r="L107">
         <f>L106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!L$2</f>
-        <v>50322309.662480868</v>
+        <v>47597460.561139829</v>
       </c>
       <c r="M107">
         <f>M106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!M$2</f>
-        <v>46811450.848819405</v>
+        <v>44276707.49873472</v>
       </c>
       <c r="N107">
         <f>N106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!N$2</f>
-        <v>43545535.673320383</v>
+        <v>41187634.882543929</v>
       </c>
       <c r="O107">
         <f>O106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!O$2</f>
-        <v>40507475.044949189</v>
+        <v>38314078.960505977</v>
       </c>
       <c r="P107">
         <f>P106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!P$2</f>
-        <v>37681372.134836458</v>
+        <v>35641003.684191607</v>
       </c>
       <c r="Q107">
         <f>Q106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Q$2</f>
-        <v>35052439.195196703</v>
+        <v>33154422.031806149</v>
       </c>
       <c r="R107">
         <f>R106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!R$2</f>
-        <v>32606920.181578334</v>
+        <v>30841322.820284791</v>
       </c>
       <c r="S107">
         <f>S106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!S$2</f>
-        <v>30332018.773561243</v>
+        <v>28689602.623520739</v>
       </c>
       <c r="T107">
         <f>T106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!T$2</f>
-        <v>28215831.417266276</v>
+        <v>26688002.440484408</v>
       </c>
       <c r="U107">
         <f>U106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!U$2</f>
-        <v>26247285.039317463</v>
+        <v>24826048.781845961</v>
       </c>
       <c r="V107">
         <f>V106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!V$2</f>
-        <v>24416079.106341828</v>
+        <v>23093998.866833456</v>
       </c>
       <c r="W107">
         <f>W106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!W$2</f>
-        <v>22712631.726829603</v>
+        <v>21482789.643566001</v>
       </c>
       <c r="X107">
         <f>X106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!X$2</f>
-        <v>21128029.513329867</v>
+        <v>19983990.366107911</v>
       </c>
       <c r="Y107">
         <f>Y106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Y$2</f>
-        <v>19653980.942632433</v>
+        <v>18589758.480100382</v>
       </c>
       <c r="Z107">
         <f>Z106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!Z$2</f>
-        <v>18282772.969890639</v>
+        <v>17292798.586139891</v>
       </c>
       <c r="AA107">
         <f>AA106/(1+'Study Parameters'!$C$4) ^'Production Cost Baseline'!AA$2</f>
-        <v>17007230.669665709</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+        <v>16086324.266176643</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>124</v>
       </c>
@@ -27408,7 +27408,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>125</v>
       </c>
@@ -27517,22 +27517,22 @@
         <v>8920460.8884980325</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>126</v>
       </c>
       <c r="B111">
         <f>SUM(B107:AA107) / SUM(C109:AA109)</f>
-        <v>2.4787770506940499</v>
-      </c>
-    </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+        <v>2.3755417565764034</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>127</v>
       </c>
       <c r="B112">
         <f>B111 * Inputs!$C$15</f>
-        <v>1.9904579717073221</v>
+        <v>1.907560030530852</v>
       </c>
     </row>
   </sheetData>
@@ -27543,19 +27543,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA112"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="11">
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -27638,12 +27638,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -27752,7 +27752,7 @@
         <v>556074856.00618696</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -27860,7 +27860,7 @@
         <v>56800000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -27969,7 +27969,7 @@
         <v>499274856.00618696</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -28078,7 +28078,7 @@
         <v>91990981.576674551</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -28186,7 +28186,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -28294,7 +28294,7 @@
         <v>12823742.755547874</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -28303,7 +28303,7 @@
         <v>8.5750117753153869</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>127</v>
       </c>
@@ -28312,12 +28312,12 @@
         <v>6.8857344555782563</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -28426,7 +28426,7 @@
         <v>483251639.09935451</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>121</v>
       </c>
@@ -28534,7 +28534,7 @@
         <v>149899999.99999997</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -28643,7 +28643,7 @@
         <v>333351639.09935451</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -28752,7 +28752,7 @@
         <v>61419765.329746507</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -28968,7 +28968,7 @@
         <v>5158976.9706227081</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -28977,7 +28977,7 @@
         <v>14.440809999857546</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>127</v>
       </c>
@@ -28986,12 +28986,12 @@
         <v>11.595970429885609</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>120</v>
       </c>
@@ -29100,7 +29100,7 @@
         <v>544180078.62649345</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>121</v>
       </c>
@@ -29208,7 +29208,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -29317,7 +29317,7 @@
         <v>463180078.62649345</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>123</v>
       </c>
@@ -29426,7 +29426,7 @@
         <v>85340548.531617671</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>124</v>
       </c>
@@ -29534,7 +29534,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -29642,7 +29642,7 @@
         <v>7075168.4168539997</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -29651,7 +29651,7 @@
         <v>14.044181815540117</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -29660,12 +29660,12 @@
         <v>11.277477997878714</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -29774,7 +29774,7 @@
         <v>488478180.27430993</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -29882,7 +29882,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -29991,7 +29991,7 @@
         <v>385278180.27430993</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>70987187.832806751</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -30208,7 +30208,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>125</v>
       </c>
@@ -30316,7 +30316,7 @@
         <v>10170554.599227624</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -30325,7 +30325,7 @@
         <v>8.2931377261665684</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -30334,12 +30334,12 @@
         <v>6.6593895941117545</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -30448,7 +30448,7 @@
         <v>529178143.97323197</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>121</v>
       </c>
@@ -30556,7 +30556,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -30665,7 +30665,7 @@
         <v>393978143.97323197</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>123</v>
       </c>
@@ -30774,7 +30774,7 @@
         <v>72590148.988806486</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>124</v>
       </c>
@@ -30882,7 +30882,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>10023155.257209834</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>126</v>
       </c>
@@ -30999,7 +30999,7 @@
         <v>8.7370834324001478</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -31008,17 +31008,17 @@
         <v>7.015877996217319</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>2050</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>120</v>
       </c>
@@ -31028,106 +31028,106 @@
       </c>
       <c r="C60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="D60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="E60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="F60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="G60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="H60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="I60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="J60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="K60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="L60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="M60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="N60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="O60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="P60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Q60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="R60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="S60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="T60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="U60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="V60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="W60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="X60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Y60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="Z60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
+        <v>263085747.37606341</v>
       </c>
       <c r="AA60" s="15">
         <f>('Cost Components'!$M$44 + 'Cost Components'!$M$42)*10^6</f>
-        <v>268701747.37606341</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+        <v>263085747.37606341</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -31235,7 +31235,7 @@
         <v>149900000</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -31245,106 +31245,106 @@
       </c>
       <c r="C62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="D62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="E62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="F62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="G62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="H62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="I62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="J62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="K62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="L62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="M62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="N62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="O62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="P62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Q62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="R62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="S62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="T62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="U62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="V62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="W62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="X62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Y62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="Z62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
+        <v>113185747.37606341</v>
       </c>
       <c r="AA62">
         <f t="shared" si="5"/>
-        <v>118801747.37606341</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+        <v>113185747.37606341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>123</v>
       </c>
@@ -31354,106 +31354,106 @@
       </c>
       <c r="C63">
         <f>C62/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>111029670.44491906</v>
+        <v>105781072.31407794</v>
       </c>
       <c r="D63">
         <f>D62/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>103766047.14478418</v>
+        <v>98860815.246801823</v>
       </c>
       <c r="E63">
         <f>E62/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>96977614.154003903</v>
+        <v>92393285.277384877</v>
       </c>
       <c r="F63">
         <f>F62/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>90633284.256078422</v>
+        <v>86348864.745219514</v>
       </c>
       <c r="G63">
         <f>G62/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>84704003.977643371</v>
+        <v>80699873.593663082</v>
       </c>
       <c r="H63">
         <f>H62/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>79162620.539853618</v>
+        <v>75420442.610900089</v>
       </c>
       <c r="I63">
         <f>I62/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>73983757.513881892</v>
+        <v>70486394.963458017</v>
       </c>
       <c r="J63">
         <f>J62/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>69143698.611104563</v>
+        <v>65875135.479867309</v>
       </c>
       <c r="K63">
         <f>K62/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>64620279.075798653</v>
+        <v>61565547.177446082</v>
       </c>
       <c r="L63">
         <f>L62/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>60392784.182989404</v>
+        <v>57537894.558360822</v>
       </c>
       <c r="M63">
         <f>M62/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>56441854.376625597</v>
+        <v>53773733.232112914</v>
       </c>
       <c r="N63">
         <f>N62/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>52749396.613668792</v>
+        <v>50255825.450572826</v>
       </c>
       <c r="O63">
         <f>O62/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>49298501.508101672</v>
+        <v>46968061.168759644</v>
       </c>
       <c r="P63">
         <f>P62/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>46073365.895422131</v>
+        <v>43895384.269868828</v>
       </c>
       <c r="Q63">
         <f>Q62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>43059220.463011332</v>
+        <v>41023723.616699837</v>
       </c>
       <c r="R63">
         <f>R62/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>40242262.114963867</v>
+        <v>38339928.613738172</v>
       </c>
       <c r="S63">
         <f>S62/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>37609590.761648469</v>
+        <v>35831708.98480203</v>
       </c>
       <c r="T63">
         <f>T62/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>35149150.244531281</v>
+        <v>33487578.490469184</v>
       </c>
       <c r="U63">
         <f>U62/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>32849673.125730168</v>
+        <v>31296802.327541292</v>
       </c>
       <c r="V63">
         <f>V62/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>30700629.089467447</v>
+        <v>29249347.96966476</v>
       </c>
       <c r="W63">
         <f>W62/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>28692176.719128456</v>
+        <v>27335839.223985758</v>
       </c>
       <c r="X63">
         <f>X62/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>26815118.429092012</v>
+        <v>25547513.293444633</v>
       </c>
       <c r="Y63">
         <f>Y62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>25060858.344945807</v>
+        <v>23876180.648079097</v>
       </c>
       <c r="Z63">
         <f>Z62/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>23421362.939201687</v>
+        <v>22314187.521569248</v>
       </c>
       <c r="AA63">
         <f>AA62/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>21889124.242244568</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+        <v>20854380.86127967</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -31561,7 +31561,7 @@
         <v>69600000</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>125</v>
       </c>
@@ -31670,30 +31670,30 @@
         <v>12823742.755547874</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>126</v>
       </c>
       <c r="B67">
         <f>SUM(B63:AA63) / SUM(C65:AA65)</f>
-        <v>2.2348536041659832</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+        <v>2.1541639489935691</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>127</v>
       </c>
       <c r="B68">
         <f>B67 * Inputs!$C$15</f>
-        <v>1.7945874441452847</v>
-      </c>
-    </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+        <v>1.7297936510418361</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>120</v>
       </c>
@@ -31703,106 +31703,106 @@
       </c>
       <c r="C71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="D71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="E71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="F71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="G71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="H71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="I71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="J71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="K71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="L71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="M71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="N71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="O71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="P71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Q71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="R71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="S71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="T71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="U71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="V71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="W71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="X71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Y71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="Z71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
+        <v>227303631.97020152</v>
       </c>
       <c r="AA71" s="15">
         <f>('Cost Components'!$N$44 + 'Cost Components'!$N$42)*10^6</f>
-        <v>232919631.97020155</v>
-      </c>
-    </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+        <v>227303631.97020152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>121</v>
       </c>
@@ -31910,7 +31910,7 @@
         <v>81000000</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>122</v>
       </c>
@@ -31920,106 +31920,106 @@
       </c>
       <c r="C73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="D73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="E73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="G73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="H73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="I73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="J73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="K73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="L73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="M73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="N73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="O73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="P73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Q73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="R73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="S73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="T73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="U73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="V73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="W73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="X73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Y73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="Z73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
+        <v>146303631.97020152</v>
       </c>
       <c r="AA73">
         <f t="shared" si="6"/>
-        <v>151919631.97020155</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+        <v>146303631.97020152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>123</v>
       </c>
@@ -32029,106 +32029,106 @@
       </c>
       <c r="C74">
         <f>C73/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>141980964.4581323</v>
+        <v>136732366.32729113</v>
       </c>
       <c r="D74">
         <f>D73/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>132692490.14778718</v>
+        <v>127787258.24980481</v>
       </c>
       <c r="E74">
         <f>E73/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>124011673.03531513</v>
+        <v>119427344.15869607</v>
       </c>
       <c r="F74">
         <f>F73/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>115898759.8460889</v>
+        <v>111614340.33522998</v>
       </c>
       <c r="G74">
         <f>G73/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>108316597.98699896</v>
+        <v>104312467.60301866</v>
       </c>
       <c r="H74">
         <f>H73/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>101230465.40841025</v>
+        <v>97488287.479456708</v>
       </c>
       <c r="I74">
         <f>I73/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>94607911.596645087</v>
+        <v>91110549.046221212</v>
       </c>
       <c r="J74">
         <f>J73/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>88418608.968827188</v>
+        <v>85150045.83758992</v>
       </c>
       <c r="K74">
         <f>K73/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>82634213.989558116</v>
+        <v>79579482.091205522</v>
       </c>
       <c r="L74">
         <f>L73/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>77228237.373418808</v>
+        <v>74373347.748790205</v>
       </c>
       <c r="M74">
         <f>M73/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>72175922.778896064</v>
+        <v>69507801.634383366</v>
       </c>
       <c r="N74">
         <f>N73/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>67454133.438220635</v>
+        <v>64960562.275124654</v>
       </c>
       <c r="O74">
         <f>O73/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>63041246.203944512</v>
+        <v>60710805.864602476</v>
       </c>
       <c r="P74">
         <f>P73/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>58917052.52705095</v>
+        <v>56739070.901497647</v>
       </c>
       <c r="Q74">
         <f>Q73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>55062665.913131721</v>
+        <v>53027169.066820219</v>
       </c>
       <c r="R74">
         <f>R73/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>51460435.432833396</v>
+        <v>49558101.931607693</v>
       </c>
       <c r="S74">
         <f>S73/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>48093864.890498497</v>
+        <v>46315983.113652043</v>
       </c>
       <c r="T74">
         <f>T73/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>44947537.280839719</v>
+        <v>43285965.52677761</v>
       </c>
       <c r="U74">
         <f>U73/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>42007044.187700666</v>
+        <v>40454173.389511786</v>
       </c>
       <c r="V74">
         <f>V73/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>39258919.801589414</v>
+        <v>37807638.681786716</v>
       </c>
       <c r="W74">
         <f>W73/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>36690579.25382188</v>
+        <v>35334241.758679174</v>
       </c>
       <c r="X74">
         <f>X73/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>34290260.984880261</v>
+        <v>33022655.849232875</v>
       </c>
       <c r="Y74">
         <f>Y73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>32046972.883065663</v>
+        <v>30862295.186198946</v>
       </c>
       <c r="Z74">
         <f>Z73/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>29950441.946790338</v>
+        <v>28843266.529157892</v>
       </c>
       <c r="AA74">
         <f>AA73/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>27991067.239990968</v>
-      </c>
-    </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+        <v>26956323.859026067</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>124</v>
       </c>
@@ -32236,7 +32236,7 @@
         <v>28000000</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>125</v>
       </c>
@@ -32345,30 +32345,30 @@
         <v>5158976.9706227081</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>126</v>
       </c>
       <c r="B78">
         <f>SUM(B74:AA74) / SUM(C76:AA76)</f>
-        <v>6.3739073570812694</v>
-      </c>
-    </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+        <v>6.1733359285098386</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>127</v>
       </c>
       <c r="B79">
         <f>B78 * Inputs!$C$15</f>
-        <v>5.1182476077362598</v>
-      </c>
-    </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+        <v>4.9571887505934003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>120</v>
       </c>
@@ -32378,106 +32378,106 @@
       </c>
       <c r="C82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="D82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="E82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="F82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="G82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="H82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="I82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="J82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="K82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="L82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="M82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="N82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="O82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="P82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Q82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="R82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="S82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="T82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="U82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="V82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="W82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="X82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Y82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="Z82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
+        <v>240060082.51392856</v>
       </c>
       <c r="AA82" s="15">
         <f>('Cost Components'!$O$44 + 'Cost Components'!$O$42)*10^6</f>
-        <v>245676082.51392856</v>
-      </c>
-    </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+        <v>240060082.51392856</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>121</v>
       </c>
@@ -32585,7 +32585,7 @@
         <v>103200000</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>122</v>
       </c>
@@ -32595,106 +32595,106 @@
       </c>
       <c r="C84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="D84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="E84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="F84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="G84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="H84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="I84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="J84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="K84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="L84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="M84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="N84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="O84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="P84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Q84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="R84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="S84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="T84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="U84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="V84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="W84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="X84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Y84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="Z84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
+        <v>136860082.51392856</v>
       </c>
       <c r="AA84">
         <f t="shared" si="7"/>
-        <v>142476082.51392856</v>
-      </c>
-    </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+        <v>136860082.51392856</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>123</v>
       </c>
@@ -32704,106 +32704,106 @@
       </c>
       <c r="C85">
         <f>C84/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>133155217.30273697</v>
+        <v>127906619.17189585</v>
       </c>
       <c r="D85">
         <f>D84/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>124444128.32031493</v>
+        <v>119538896.42233257</v>
       </c>
       <c r="E85">
         <f>E84/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>116302923.66384572</v>
+        <v>111718594.78722669</v>
       </c>
       <c r="F85">
         <f>F84/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>108694321.18116423</v>
+        <v>104409901.67030533</v>
       </c>
       <c r="G85">
         <f>G84/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>101583477.73940581</v>
+        <v>97579347.355425537</v>
       </c>
       <c r="H85">
         <f>H84/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>94937829.662996098</v>
+        <v>91195651.734042555</v>
       </c>
       <c r="I85">
         <f>I84/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>88726943.610276714</v>
+        <v>85229581.059852853</v>
       </c>
       <c r="J85">
         <f>J84/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>82922377.205866098</v>
+        <v>79653814.07462883</v>
       </c>
       <c r="K85">
         <f>K84/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>77497548.790529057</v>
+        <v>74442816.892176479</v>
       </c>
       <c r="L85">
         <f>L84/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>72427615.692083225</v>
+        <v>69572726.067454651</v>
       </c>
       <c r="M85">
         <f>M84/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>67689360.459890857</v>
+        <v>65021239.315378174</v>
       </c>
       <c r="N85">
         <f>N84/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>63261084.541954085</v>
+        <v>60767513.378858119</v>
       </c>
       <c r="O85">
         <f>O84/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>59122508.917714097</v>
+        <v>56792068.578372069</v>
       </c>
       <c r="P85">
         <f>P84/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>55254681.231508501</v>
+        <v>53076699.605955206</v>
       </c>
       <c r="Q85">
         <f>Q84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>51639889.001409806</v>
+        <v>49604392.155098319</v>
       </c>
       <c r="R85">
         <f>R84/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>48261578.505990483</v>
+        <v>46359245.004764788</v>
       </c>
       <c r="S85">
         <f>S84/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>45104278.977561198</v>
+        <v>43326397.200714752</v>
       </c>
       <c r="T85">
         <f>T84/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>42153531.75473009</v>
+        <v>40491960.000667997</v>
       </c>
       <c r="U85">
         <f>U84/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>39395824.069841206</v>
+        <v>37842953.271652326</v>
       </c>
       <c r="V85">
         <f>V84/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>36818527.168075897</v>
+        <v>35367246.048273206</v>
       </c>
       <c r="W85">
         <f>W84/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>34409838.474837281</v>
+        <v>33053500.979694586</v>
       </c>
       <c r="X85">
         <f>X84/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>32158727.546576899</v>
+        <v>30891122.41092952</v>
       </c>
       <c r="Y85">
         <f>Y84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>30054885.557548504</v>
+        <v>28870207.860681795</v>
       </c>
       <c r="Z85">
         <f>Z84/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>28088678.091166824</v>
+        <v>26981502.673534386</v>
       </c>
       <c r="AA85">
         <f>AA84/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>26251101.019782078</v>
-      </c>
-    </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+        <v>25216357.63881718</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>124</v>
       </c>
@@ -32911,7 +32911,7 @@
         <v>38400000</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>125</v>
       </c>
@@ -33020,30 +33020,30 @@
         <v>7075168.4168539997</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>126</v>
       </c>
       <c r="B89">
         <f>SUM(B85:AA85) / SUM(C87:AA87)</f>
-        <v>4.4289777305232976</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+        <v>4.2827277305232974</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>127</v>
       </c>
       <c r="B90">
         <f>B89 * Inputs!$C$15</f>
-        <v>3.5564691176102081</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+        <v>3.4390303676102079</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -33053,106 +33053,106 @@
       </c>
       <c r="C93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="D93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="E93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="F93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="G93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="H93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="I93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="J93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="K93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="L93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="M93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="N93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="O93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="P93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Q93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="R93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="S93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="T93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="U93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="V93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="W93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="X93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Y93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="Z93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
+        <v>215695187.23464701</v>
       </c>
       <c r="AA93" s="15">
         <f>('Cost Components'!$P$44 + 'Cost Components'!$P$42)*10^6</f>
-        <v>221311187.23464698</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+        <v>215695187.23464701</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -33260,7 +33260,7 @@
         <v>135200000</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -33270,106 +33270,106 @@
       </c>
       <c r="C95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="D95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="E95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="F95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="G95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="H95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="I95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="J95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="K95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="L95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="M95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="N95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="O95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="P95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Q95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="R95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="S95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="T95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="U95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="V95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="W95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="X95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Y95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="Z95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
+        <v>80495187.234647006</v>
       </c>
       <c r="AA95">
         <f t="shared" si="8"/>
-        <v>86111187.234646976</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+        <v>80495187.234647006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -33379,106 +33379,106 @@
       </c>
       <c r="C96">
         <f>C95/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>80477745.079109326</v>
+        <v>75229146.94826822</v>
       </c>
       <c r="D96">
         <f>D95/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>75212845.86832647</v>
+        <v>70307613.970344141</v>
       </c>
       <c r="E96">
         <f>E95/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>70292379.316192955</v>
+        <v>65708050.439573959</v>
       </c>
       <c r="F96">
         <f>F95/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>65693812.445040151</v>
+        <v>61409392.934181273</v>
       </c>
       <c r="G96">
         <f>G95/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>61396086.397233777</v>
+        <v>57391956.013253517</v>
       </c>
       <c r="H96">
         <f>H95/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>57379519.997414753</v>
+        <v>53637342.068461239</v>
       </c>
       <c r="I96">
         <f>I95/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>53625719.623752102</v>
+        <v>50128357.073328257</v>
       </c>
       <c r="J96">
         <f>J95/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>50117494.975469254</v>
+        <v>46848931.844232015</v>
       </c>
       <c r="K96">
         <f>K95/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>46838780.350905843</v>
+        <v>43784048.45255328</v>
       </c>
       <c r="L96">
         <f>L95/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>43774561.07561294</v>
+        <v>40919671.450984381</v>
       </c>
       <c r="M96">
         <f>M95/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>40910804.743563488</v>
+        <v>38242683.599050812</v>
       </c>
       <c r="N96">
         <f>N95/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>38234396.956601396</v>
+        <v>35740825.793505445</v>
       </c>
       <c r="O96">
         <f>O95/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>35733081.26785177</v>
+        <v>33402640.928509757</v>
       </c>
       <c r="P96">
         <f>P95/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>33395403.054067079</v>
+        <v>31217421.428513791</v>
       </c>
       <c r="Q96">
         <f>Q95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>31210657.059875768</v>
+        <v>29175160.213564288</v>
       </c>
       <c r="R96">
         <f>R95/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>29168838.373715676</v>
+        <v>27266504.872489993</v>
       </c>
       <c r="S96">
         <f>S95/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>27260596.610949229</v>
+        <v>25482714.834102798</v>
       </c>
       <c r="T96">
         <f>T95/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>25477193.094345074</v>
+        <v>23815621.340282988</v>
       </c>
       <c r="U96">
         <f>U95/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>23810460.835836515</v>
+        <v>22257590.03764765</v>
       </c>
       <c r="V96">
         <f>V95/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>22252767.13629581</v>
+        <v>20801486.016493134</v>
       </c>
       <c r="W96">
         <f>W95/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>20796978.632052157</v>
+        <v>19440641.13690947</v>
       </c>
       <c r="X96">
         <f>X95/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>19436428.628086131</v>
+        <v>18168823.492438756</v>
       </c>
       <c r="Y96">
         <f>Y95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>18164886.568304796</v>
+        <v>16980208.87143809</v>
       </c>
       <c r="Z96">
         <f>Z95/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>16976529.503088593</v>
+        <v>15869354.085456157</v>
       </c>
       <c r="AA96">
         <f>AA95/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>15865915.423447281</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+        <v>14831172.042482389</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -33586,7 +33586,7 @@
         <v>55200000</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -33695,30 +33695,30 @@
         <v>10170554.599227624</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
       <c r="B100">
         <f>SUM(B96:AA96) / SUM(C98:AA98)</f>
-        <v>2.0869737784864602</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+        <v>1.9852346480516783</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>127</v>
       </c>
       <c r="B101">
         <f>B100 * Inputs!$C$15</f>
-        <v>1.6758399441246277</v>
-      </c>
-    </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+        <v>1.5941434223854978</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>120</v>
       </c>
@@ -33728,106 +33728,106 @@
       </c>
       <c r="C104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="D104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="E104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="F104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="G104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="H104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="I104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="J104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="K104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="L104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="M104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="N104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="O104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="P104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Q104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="R104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="S104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="T104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="U104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="V104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="W104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="X104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Y104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="Z104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
+        <v>231799868.49539924</v>
       </c>
       <c r="AA104" s="15">
         <f>('Cost Components'!$Q$44 + 'Cost Components'!$Q$42)*10^6</f>
-        <v>237415868.49539927</v>
-      </c>
-    </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+        <v>231799868.49539924</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>121</v>
       </c>
@@ -33935,7 +33935,7 @@
         <v>133699999.99999999</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>122</v>
       </c>
@@ -33945,106 +33945,106 @@
       </c>
       <c r="C106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="D106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="E106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="F106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="G106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="H106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="I106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="J106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="K106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="L106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="M106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="N106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="O106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="P106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Q106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="R106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="S106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="T106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="U106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="V106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="W106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="X106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Y106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="Z106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
+        <v>98099868.495399252</v>
       </c>
       <c r="AA106">
         <f t="shared" si="9"/>
-        <v>103715868.49539928</v>
-      </c>
-    </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+        <v>98099868.495399252</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>123</v>
       </c>
@@ -34054,106 +34054,106 @@
       </c>
       <c r="C107">
         <f>C106/(1+Inputs!$C$5) ^'Production Cost Baseline'!C$2</f>
-        <v>96930718.219999328</v>
+        <v>91682120.089158177</v>
       </c>
       <c r="D107">
         <f>D106/(1+Inputs!$C$5) ^'Production Cost Baseline'!D$2</f>
-        <v>90589456.280373201</v>
+        <v>85684224.382390812</v>
       </c>
       <c r="E107">
         <f>E106/(1+Inputs!$C$5) ^'Production Cost Baseline'!E$2</f>
-        <v>84663043.252685234</v>
+        <v>80078714.376066178</v>
       </c>
       <c r="F107">
         <f>F106/(1+Inputs!$C$5) ^'Production Cost Baseline'!F$2</f>
-        <v>79124339.48849088</v>
+        <v>74839919.977631956</v>
       </c>
       <c r="G107">
         <f>G106/(1+Inputs!$C$5) ^'Production Cost Baseline'!G$2</f>
-        <v>73947980.8303653</v>
+        <v>69943850.446384996</v>
       </c>
       <c r="H107">
         <f>H106/(1+Inputs!$C$5) ^'Production Cost Baseline'!H$2</f>
-        <v>69110262.458285332</v>
+        <v>65368084.529331774</v>
       </c>
       <c r="I107">
         <f>I106/(1+Inputs!$C$5) ^'Production Cost Baseline'!I$2</f>
-        <v>64589030.334846094</v>
+        <v>61091667.784422219</v>
       </c>
       <c r="J107">
         <f>J106/(1+Inputs!$C$5) ^'Production Cost Baseline'!J$2</f>
-        <v>60363579.752192616</v>
+        <v>57095016.620955341</v>
       </c>
       <c r="K107">
         <f>K106/(1+Inputs!$C$5) ^'Production Cost Baseline'!K$2</f>
-        <v>56414560.516067863</v>
+        <v>53359828.617715269</v>
       </c>
       <c r="L107">
         <f>L106/(1+Inputs!$C$5) ^'Production Cost Baseline'!L$2</f>
-        <v>52723888.3327737</v>
+        <v>49868998.708145112</v>
       </c>
       <c r="M107">
         <f>M106/(1+Inputs!$C$5) ^'Production Cost Baseline'!M$2</f>
-        <v>49274661.993246444</v>
+        <v>46606540.848733746</v>
       </c>
       <c r="N107">
         <f>N106/(1+Inputs!$C$5) ^'Production Cost Baseline'!N$2</f>
-        <v>46051085.974996686</v>
+        <v>43557514.811900705</v>
       </c>
       <c r="O107">
         <f>O106/(1+Inputs!$C$5) ^'Production Cost Baseline'!O$2</f>
-        <v>43038398.107473537</v>
+        <v>40707957.768131495</v>
       </c>
       <c r="P107">
         <f>P106/(1+Inputs!$C$5) ^'Production Cost Baseline'!P$2</f>
-        <v>40222801.969601437</v>
+        <v>38044820.344048128</v>
       </c>
       <c r="Q107">
         <f>Q106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Q$2</f>
-        <v>37591403.709907882</v>
+        <v>35555906.86359638</v>
       </c>
       <c r="R107">
         <f>R106/(1+Inputs!$C$5) ^'Production Cost Baseline'!R$2</f>
-        <v>35132152.999913909</v>
+        <v>33229819.49868821</v>
       </c>
       <c r="S107">
         <f>S106/(1+Inputs!$C$5) ^'Production Cost Baseline'!S$2</f>
-        <v>32833787.850386832</v>
+        <v>31055906.073540382</v>
       </c>
       <c r="T107">
         <f>T106/(1+Inputs!$C$5) ^'Production Cost Baseline'!T$2</f>
-        <v>30685783.037744705</v>
+        <v>29024211.2836826</v>
       </c>
       <c r="U107">
         <f>U106/(1+Inputs!$C$5) ^'Production Cost Baseline'!U$2</f>
-        <v>28678301.904434301</v>
+        <v>27125431.106245417</v>
       </c>
       <c r="V107">
         <f>V106/(1+Inputs!$C$5) ^'Production Cost Baseline'!V$2</f>
-        <v>26802151.312555421</v>
+        <v>25350870.19275273</v>
       </c>
       <c r="W107">
         <f>W106/(1+Inputs!$C$5) ^'Production Cost Baseline'!W$2</f>
-        <v>25048739.544444319</v>
+        <v>23692402.049301613</v>
       </c>
       <c r="X107">
         <f>X106/(1+Inputs!$C$5) ^'Production Cost Baseline'!X$2</f>
-        <v>23410036.957424596</v>
+        <v>22142431.82177721</v>
       </c>
       <c r="Y107">
         <f>Y106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Y$2</f>
-        <v>21878539.212546352</v>
+        <v>20693861.515679635</v>
       </c>
       <c r="Z107">
         <f>Z106/(1+Inputs!$C$5) ^'Production Cost Baseline'!Z$2</f>
-        <v>20447232.908921823</v>
+        <v>19340057.491289377</v>
       </c>
       <c r="AA107">
         <f>AA106/(1+Inputs!$C$5) ^'Production Cost Baseline'!AA$2</f>
-        <v>19109563.466282077</v>
-      </c>
-    </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.25">
+        <v>18074820.085317176</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>124</v>
       </c>
@@ -34261,7 +34261,7 @@
         <v>54400000</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>125</v>
       </c>
@@ -34370,22 +34370,22 @@
         <v>10023155.257209834</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>126</v>
       </c>
       <c r="B111">
         <f>SUM(B107:AA107) / SUM(C109:AA109)</f>
-        <v>2.4538992274075415</v>
-      </c>
-    </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+        <v>2.3506639332898938</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>127</v>
       </c>
       <c r="B112">
         <f>B111 * Inputs!$C$15</f>
-        <v>1.9704810796082559</v>
+        <v>1.8875831384317847</v>
       </c>
     </row>
   </sheetData>
@@ -34396,9 +34396,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B10A8B-634A-6442-9417-F0F1FBDE8D91}">
   <dimension ref="A1:AA24"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -34481,12 +34481,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -34594,7 +34594,7 @@
         <v>54.562814434725944</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -34702,7 +34702,7 @@
         <v>26.354791572862013</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -34786,7 +34786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -34894,12 +34894,12 @@
         <v>23.860268489130025</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>137</v>
       </c>
@@ -34908,7 +34908,7 @@
         <v>0.40610761007463636</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>98</v>
       </c>
@@ -34917,7 +34917,7 @@
         <v>0.19615706283762402</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -34926,7 +34926,7 @@
         <v>0.22014484330776898</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -34935,12 +34935,12 @@
         <v>0.17759048377997066</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2050</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>137</v>
       </c>
@@ -34949,106 +34949,106 @@
       </c>
       <c r="C15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!C1</f>
-        <v>105.57757009345794</v>
+        <v>100.32897196261682</v>
       </c>
       <c r="D15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!D1</f>
-        <v>98.670626255568166</v>
+        <v>93.765394357585819</v>
       </c>
       <c r="E15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!E1</f>
-        <v>92.215538556605765</v>
+        <v>87.631209679986739</v>
       </c>
       <c r="F15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!F1</f>
-        <v>86.182746314584833</v>
+        <v>81.898326803725936</v>
       </c>
       <c r="G15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!G1</f>
-        <v>80.544622723911047</v>
+        <v>76.540492339930765</v>
       </c>
       <c r="H15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!H1</f>
-        <v>75.27534834010379</v>
+        <v>71.533170411150252</v>
       </c>
       <c r="I15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!I1</f>
-        <v>70.350792841218492</v>
+        <v>66.853430290794634</v>
       </c>
       <c r="J15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!J1</f>
-        <v>65.748404524503258</v>
+        <v>62.479841393266007</v>
       </c>
       <c r="K15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!K1</f>
-        <v>61.447107032246031</v>
+        <v>58.392375133893459</v>
       </c>
       <c r="L15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!L1</f>
-        <v>57.427202833874802</v>
+        <v>54.572313209246225</v>
       </c>
       <c r="M15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!M1</f>
-        <v>53.670283022312894</v>
+        <v>51.002161877800205</v>
       </c>
       <c r="N15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!N1</f>
-        <v>50.159143011507382</v>
+        <v>47.665571848411417</v>
       </c>
       <c r="O15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!O1</f>
-        <v>46.877703749072317</v>
+        <v>44.547263409730292</v>
       </c>
       <c r="P15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!P1</f>
-        <v>43.810938083245162</v>
+        <v>41.632956457691861</v>
       </c>
       <c r="Q15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Q1</f>
-        <v>40.944801946958087</v>
+        <v>38.909305100646598</v>
       </c>
       <c r="R15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!R1</f>
-        <v>38.266170043886071</v>
+        <v>36.363836542660373</v>
       </c>
       <c r="S15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!S1</f>
-        <v>35.762775741949596</v>
+        <v>33.984893965103154</v>
       </c>
       <c r="T15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!T1</f>
-        <v>33.423154899018314</v>
+        <v>31.761583144956219</v>
       </c>
       <c r="U15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!U1</f>
-        <v>31.236593363568517</v>
+        <v>29.683722565379643</v>
       </c>
       <c r="V15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!V1</f>
-        <v>29.193077909877122</v>
+        <v>27.741796790074435</v>
       </c>
       <c r="W15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!W1</f>
-        <v>27.283250383062729</v>
+        <v>25.926912887920029</v>
       </c>
       <c r="X15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!X1</f>
-        <v>25.498364843983857</v>
+        <v>24.230759708336478</v>
       </c>
       <c r="Y15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Y1</f>
-        <v>23.830247517741924</v>
+        <v>22.645569820875213</v>
       </c>
       <c r="Z15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!Z1</f>
-        <v>22.271259362375627</v>
+        <v>21.164083944743187</v>
       </c>
       <c r="AA15" s="8">
         <f>('Cost Components'!$M$42) / (1+Inputs!$C$5)^'Cost Breakdown'!AA1</f>
-        <v>20.814261086332362</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+        <v>19.779517705367464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>98</v>
       </c>
@@ -35156,7 +35156,7 @@
         <v>4.8335463773658898</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -35240,7 +35240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -35348,45 +35348,45 @@
         <v>23.860268489130025</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>137</v>
       </c>
       <c r="B21" s="17">
         <f>SUM(B15:AA15) / SUM($B$15:$AA$18)</f>
-        <v>0.35519748239815635</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.3436068922203015</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>98</v>
       </c>
       <c r="B22" s="17">
         <f t="shared" ref="B22:B24" si="1">SUM(B16:AA16) / SUM($B$15:$AA$18)</f>
-        <v>8.2484960536142585E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+        <v>8.3967661591601739E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>76</v>
       </c>
       <c r="B23" s="17">
         <f t="shared" si="1"/>
-        <v>0.15513964853796511</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+        <v>0.15792834746120712</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="17">
         <f t="shared" si="1"/>
-        <v>0.40717790852773578</v>
+        <v>0.41449709872688956</v>
       </c>
     </row>
   </sheetData>
@@ -35397,13 +35397,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AH21"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>139</v>
       </c>
@@ -35445,7 +35445,7 @@
       <c r="AG1" s="22"/>
       <c r="AH1" s="22"/>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -35537,7 +35537,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>148</v>
       </c>
@@ -35649,7 +35649,7 @@
         <v>7.015877996217319</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>148</v>
       </c>
@@ -35761,7 +35761,7 @@
         <v>6.3142901965955875</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>150</v>
       </c>
@@ -35873,7 +35873,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>151</v>
       </c>
@@ -35985,7 +35985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>153</v>
       </c>
@@ -36097,7 +36097,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>154</v>
       </c>
@@ -36209,7 +36209,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>154</v>
       </c>
@@ -36321,7 +36321,7 @@
         <v>3076.9675200000006</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>156</v>
       </c>
@@ -36433,7 +36433,7 @@
         <v>1792.1184285349839</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>157</v>
       </c>
@@ -36475,7 +36475,7 @@
       <c r="AG12" s="22"/>
       <c r="AH12" s="22"/>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
@@ -36567,7 +36567,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>148</v>
       </c>
@@ -36584,11 +36584,11 @@
       </c>
       <c r="E14" s="13">
         <f>'CO2 Corrected Production Cost'!B68</f>
-        <v>1.8138553613795019</v>
+        <v>1.7490615682760537</v>
       </c>
       <c r="F14" s="13">
         <f>'WACC Corrected Production Cost'!B68</f>
-        <v>1.7945874441452847</v>
+        <v>1.7297936510418361</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>148</v>
@@ -36606,11 +36606,11 @@
       </c>
       <c r="L14" s="13">
         <f>'CO2 Corrected Production Cost'!B79</f>
-        <v>5.1528542630059722</v>
+        <v>4.9917954058631144</v>
       </c>
       <c r="M14" s="13">
         <f>'WACC Corrected Production Cost'!B79</f>
-        <v>5.1182476077362598</v>
+        <v>4.9571887505934003</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>148</v>
@@ -36628,11 +36628,11 @@
       </c>
       <c r="S14" s="13">
         <f>'CO2 Corrected Production Cost'!B90</f>
-        <v>3.5826981436630465</v>
+        <v>3.4652593936630463</v>
       </c>
       <c r="T14" s="13">
         <f>'WACC Corrected Production Cost'!B90</f>
-        <v>3.5564691176102081</v>
+        <v>3.4390303676102079</v>
       </c>
       <c r="V14" s="12" t="s">
         <v>148</v>
@@ -36650,11 +36650,11 @@
       </c>
       <c r="Z14" s="13">
         <f>'CO2 Corrected Production Cost'!B101</f>
-        <v>1.6950734285111995</v>
+        <v>1.6133769067720696</v>
       </c>
       <c r="AA14" s="13">
         <f>'WACC Corrected Production Cost'!B101</f>
-        <v>1.6758399441246277</v>
+        <v>1.5941434223854978</v>
       </c>
       <c r="AC14" s="12" t="s">
         <v>148</v>
@@ -36672,14 +36672,14 @@
       </c>
       <c r="AG14" s="13">
         <f>'CO2 Corrected Production Cost'!B112</f>
-        <v>1.9904579717073221</v>
+        <v>1.907560030530852</v>
       </c>
       <c r="AH14" s="13">
         <f>'WACC Corrected Production Cost'!B112</f>
-        <v>1.9704810796082559</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1.8875831384317847</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>148</v>
       </c>
@@ -36696,11 +36696,11 @@
       </c>
       <c r="E15" s="16">
         <f>E14*Inputs!$C$6</f>
-        <v>1.6324698252415517</v>
+        <v>1.5741554114484484</v>
       </c>
       <c r="F15" s="16">
         <f>F14*Inputs!$C$6</f>
-        <v>1.6151286997307563</v>
+        <v>1.5568142859376526</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>148</v>
@@ -36718,11 +36718,11 @@
       </c>
       <c r="L15" s="16">
         <f>L14*Inputs!$C$6</f>
-        <v>4.6375688367053751</v>
+        <v>4.4926158652768029</v>
       </c>
       <c r="M15" s="16">
         <f>M14*Inputs!$C$6</f>
-        <v>4.6064228469626336</v>
+        <v>4.4614698755340605</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>148</v>
@@ -36740,11 +36740,11 @@
       </c>
       <c r="S15" s="16">
         <f>S14*Inputs!$C$6</f>
-        <v>3.2244283292967419</v>
+        <v>3.1187334542967418</v>
       </c>
       <c r="T15" s="16">
         <f>T14*Inputs!$C$6</f>
-        <v>3.2008222058491875</v>
+        <v>3.0951273308491873</v>
       </c>
       <c r="V15" s="12" t="s">
         <v>148</v>
@@ -36762,11 +36762,11 @@
       </c>
       <c r="Z15" s="16">
         <f>Z14*Inputs!$C$6</f>
-        <v>1.5255660856600795</v>
+        <v>1.4520392160948628</v>
       </c>
       <c r="AA15" s="16">
         <f>AA14*Inputs!$C$6</f>
-        <v>1.508255949712165</v>
+        <v>1.4347290801469481</v>
       </c>
       <c r="AC15" s="12" t="s">
         <v>148</v>
@@ -36784,14 +36784,14 @@
       </c>
       <c r="AG15" s="16">
         <f>AG14*Inputs!$C$6</f>
-        <v>1.7914121745365899</v>
+        <v>1.7168040274777667</v>
       </c>
       <c r="AH15" s="16">
         <f>AH14*Inputs!$C$6</f>
-        <v>1.7734329716474304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+        <v>1.6988248245886062</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>150</v>
       </c>
@@ -36903,7 +36903,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>151</v>
       </c>
@@ -37015,7 +37015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>153</v>
       </c>
@@ -37127,7 +37127,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>154</v>
       </c>
@@ -37239,7 +37239,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>154</v>
       </c>
@@ -37351,7 +37351,7 @@
         <v>3076.9675200000006</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>156</v>
       </c>
@@ -37368,11 +37368,11 @@
       </c>
       <c r="E21" s="13">
         <f>(E15-E16) / E20 * 10^6</f>
-        <v>-21.946989794175089</v>
+        <v>-40.898900535534914</v>
       </c>
       <c r="F21" s="13">
         <f>(F15-F16) / F20 * 10^6</f>
-        <v>-27.582774181913884</v>
+        <v>-46.534684923273851</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>156</v>
@@ -37390,11 +37390,11 @@
       </c>
       <c r="L21" s="13">
         <f>(L15-L16) / L20 * 10^6</f>
-        <v>954.69608229903395</v>
+        <v>907.5870470276534</v>
       </c>
       <c r="M21" s="13">
         <f>(M15-M16) / M20 * 10^6</f>
-        <v>944.5737818391508</v>
+        <v>897.46474656777002</v>
       </c>
       <c r="O21" s="12" t="s">
         <v>156</v>
@@ -37412,11 +37412,11 @@
       </c>
       <c r="S21" s="13">
         <f>(S15-S16) / S20 * 10^6</f>
-        <v>495.43205100089642</v>
+        <v>461.08171278218157</v>
       </c>
       <c r="T21" s="13">
         <f>(T15-T16) / T20 * 10^6</f>
-        <v>487.7601716930659</v>
+        <v>453.4098334743511</v>
       </c>
       <c r="V21" s="12" t="s">
         <v>156</v>
@@ -37434,11 +37434,11 @@
       </c>
       <c r="Z21" s="13">
         <f>(Z15-Z16) / Z20 * 10^6</f>
-        <v>-56.690203327177294</v>
+        <v>-80.586090783674294</v>
       </c>
       <c r="AA21" s="13">
         <f>(AA15-AA16) / AA20 * 10^6</f>
-        <v>-62.315916252451991</v>
+        <v>-86.211803708949063</v>
       </c>
       <c r="AC21" s="12" t="s">
         <v>156</v>
@@ -37456,11 +37456,11 @@
       </c>
       <c r="AG21" s="13">
         <f>(AG15-AG16) / AG20 * 10^6</f>
-        <v>29.708527614418848</v>
+        <v>5.4612300482673817</v>
       </c>
       <c r="AH21" s="13">
         <f>(AH15-AH16) / AH20 * 10^6</f>
-        <v>23.865371073995103</v>
+        <v>-0.38192649215672592</v>
       </c>
     </row>
   </sheetData>
